--- a/recursos/Cotizador Backlight.xlsx
+++ b/recursos/Cotizador Backlight.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bruno\app_mama\empresa_app\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bruno\app_mama\empresa_app\recursos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF77C21C-D456-4A33-BC91-03A54DC1B3CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F3B9416-B364-416F-9C9C-96AD2BF4D3B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="6" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Valores" sheetId="1" state="hidden" r:id="rId1"/>
@@ -94,7 +94,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1091" uniqueCount="636">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1095" uniqueCount="637">
   <si>
     <t>Nº:</t>
   </si>
@@ -1121,9 +1121,6 @@
     <t>M12</t>
   </si>
   <si>
-    <t>Led Lateral Actilum M12 -6k, 90 cms max 1000mm</t>
-  </si>
-  <si>
     <t>basic 9 focos</t>
   </si>
   <si>
@@ -2038,6 +2035,12 @@
   </si>
   <si>
     <t>2 FP 350 watts - 24v MEAN WELL</t>
+  </si>
+  <si>
+    <t>Watts</t>
+  </si>
+  <si>
+    <t>Led Lateral Actilum M12 -6k, 60 cms max 1000mm</t>
   </si>
 </sst>
 </file>
@@ -5193,13 +5196,178 @@
     <xf numFmtId="0" fontId="16" fillId="18" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="14" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="49" fillId="3" borderId="0" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="48" fillId="4" borderId="0" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="174" fontId="34" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="174" fontId="34" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="174" fontId="34" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="58" fillId="12" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="58" fillId="12" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="58" fillId="12" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="58" fillId="12" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="4" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="42" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="42" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="42" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="42" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="3" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="3" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="64" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="63" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="3" borderId="77" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="3" borderId="78" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="3" borderId="34" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="22" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="22" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="22" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="18" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="18" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5209,6 +5377,9 @@
     <xf numFmtId="0" fontId="14" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="97" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="97" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5245,87 +5416,35 @@
     <xf numFmtId="0" fontId="98" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="22" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="22" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="22" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="18" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="25" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="91" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="56" fillId="18" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="26" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="97" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="176" fontId="89" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="57" fillId="4" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="3" borderId="34" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="75" fillId="3" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="75" fillId="3" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="64" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="63" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="75" fillId="3" borderId="77" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="75" fillId="3" borderId="78" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="89" fillId="0" borderId="68" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="85" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -5340,9 +5459,6 @@
     </xf>
     <xf numFmtId="0" fontId="43" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="79" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5364,120 +5480,13 @@
     <xf numFmtId="0" fontId="81" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="81" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="81" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="43" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="25" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="91" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="86" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="26" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="176" fontId="89" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="57" fillId="4" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="89" fillId="0" borderId="68" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="49" fillId="3" borderId="0" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="43" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="48" fillId="4" borderId="0" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="174" fontId="34" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="174" fontId="34" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="174" fontId="34" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="58" fillId="12" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="58" fillId="12" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="58" fillId="12" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="58" fillId="12" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="43" fillId="4" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="42" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="42" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="42" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="42" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5486,15 +5495,39 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -5531,39 +5564,6 @@
     <xf numFmtId="166" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -5574,6 +5574,36 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="69" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="69" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="69" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="69" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -5590,36 +5620,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
-    <xf numFmtId="1" fontId="69" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="69" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="69" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="69" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="69" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="69" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="69" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="69" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="69" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="29" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5684,6 +5684,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -6772,523 +6775,6 @@
     </dxf>
     <dxf>
       <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="16"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="16"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="167" formatCode="0.000"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="16"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="167" formatCode="0.000"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="16"/>
-        <color indexed="8"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="175" formatCode="_-&quot;$&quot;* #,##0_-;\-&quot;$&quot;* #,##0_-;_-&quot;$&quot;* &quot;-&quot;???_-;_-@_-"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="16"/>
-        <color indexed="8"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="167" formatCode="0.000"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="16"/>
-        <color indexed="8"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="167" formatCode="0.000"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="16"/>
-        <color indexed="8"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="167" formatCode="0.000"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="16"/>
-        <color indexed="8"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="167" formatCode="0.000"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="16"/>
-        <color indexed="8"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="167" formatCode="0.000"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor indexed="9"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="16"/>
-        <color indexed="63"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="167" formatCode="0.000"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor indexed="9"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="16"/>
-        <color indexed="63"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="167" formatCode="0.000"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor indexed="9"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="16"/>
-        <color indexed="63"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor indexed="9"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="16"/>
-        <color indexed="63"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor indexed="9"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="medium">
-          <color auto="1"/>
-        </left>
-        <right style="medium">
-          <color auto="1"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="16"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
         <b/>
         <i val="0"/>
         <strike val="0"/>
@@ -7622,6 +7108,392 @@
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
           <bgColor theme="7" tint="-0.249977111117893"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color indexed="8"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="169" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color indexed="8"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="169" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color indexed="8"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="167" formatCode="0.000"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color indexed="8"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="167" formatCode="0.000"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color indexed="8"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="167" formatCode="0.000"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color indexed="63"/>
+        <name val="Copperplate Light"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color indexed="8"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color indexed="63"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="medium">
+          <color auto="1"/>
+        </left>
+        <right style="medium">
+          <color auto="1"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color indexed="63"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -8211,7 +8083,39 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
         <i val="0"/>
         <strike val="0"/>
         <condense val="0"/>
@@ -8220,20 +8124,20 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color indexed="8"/>
+        <sz val="16"/>
+        <color theme="1"/>
         <name val="Calibri"/>
         <family val="2"/>
-        <scheme val="none"/>
+        <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="169" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+      <numFmt numFmtId="167" formatCode="0.000"/>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
-          <bgColor theme="0"/>
+          <bgColor theme="5" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color auto="1"/>
@@ -8245,13 +8149,11 @@
         <bottom style="thin">
           <color auto="1"/>
         </bottom>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
+        <b/>
         <i val="0"/>
         <strike val="0"/>
         <condense val="0"/>
@@ -8260,142 +8162,20 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color indexed="8"/>
+        <sz val="16"/>
+        <color theme="1"/>
         <name val="Calibri"/>
         <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="169" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color indexed="8"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
+        <scheme val="minor"/>
       </font>
       <numFmt numFmtId="167" formatCode="0.000"/>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
-          <bgColor theme="0"/>
+          <bgColor theme="5" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color indexed="8"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="167" formatCode="0.000"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color indexed="8"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="167" formatCode="0.000"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color auto="1"/>
@@ -8423,36 +8203,30 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="16"/>
-        <color indexed="63"/>
-        <name val="Copperplate Light"/>
+        <color indexed="8"/>
+        <name val="Arial"/>
+        <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <numFmt numFmtId="175" formatCode="_-&quot;$&quot;* #,##0_-;\-&quot;$&quot;* #,##0_-;_-&quot;$&quot;* &quot;-&quot;???_-;_-@_-"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
-          <color indexed="64"/>
+          <color auto="1"/>
         </left>
         <right style="thin">
-          <color indexed="64"/>
+          <color auto="1"/>
         </right>
         <top style="thin">
-          <color indexed="64"/>
+          <color auto="1"/>
         </top>
         <bottom style="thin">
-          <color indexed="64"/>
+          <color auto="1"/>
         </bottom>
       </border>
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
+        <b/>
         <i val="0"/>
         <strike val="0"/>
         <condense val="0"/>
@@ -8461,20 +8235,276 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="12"/>
+        <sz val="16"/>
         <color indexed="8"/>
-        <name val="Calibri"/>
+        <name val="Arial"/>
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="1" formatCode="0"/>
+      <numFmt numFmtId="167" formatCode="0.000"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color indexed="8"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="167" formatCode="0.000"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color indexed="8"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="167" formatCode="0.000"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color indexed="8"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="167" formatCode="0.000"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color indexed="8"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="167" formatCode="0.000"/>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
-          <bgColor theme="0"/>
+          <bgColor indexed="9"/>
         </patternFill>
       </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color indexed="63"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="167" formatCode="0.000"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor indexed="9"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color indexed="63"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="167" formatCode="0.000"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor indexed="9"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color indexed="63"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor indexed="9"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color auto="1"/>
@@ -8492,7 +8522,7 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
+        <b/>
         <i val="0"/>
         <strike val="0"/>
         <condense val="0"/>
@@ -8501,9 +8531,9 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="12"/>
+        <sz val="16"/>
         <color indexed="63"/>
-        <name val="Calibri"/>
+        <name val="Arial"/>
         <family val="2"/>
         <scheme val="none"/>
       </font>
@@ -8511,11 +8541,11 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
-          <bgColor theme="0"/>
+          <bgColor indexed="9"/>
         </patternFill>
       </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left/>
         <right style="thin">
           <color auto="1"/>
@@ -8526,15 +8556,6 @@
         <bottom style="thin">
           <color auto="1"/>
         </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color auto="1"/>
-        </top>
       </border>
     </dxf>
     <dxf>
@@ -8554,46 +8575,28 @@
       </border>
     </dxf>
     <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+      </font>
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <i val="0"/>
         <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="12"/>
-        <color indexed="63"/>
-        <name val="Calibri"/>
+        <color theme="1"/>
+        <name val="Arial"/>
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
     </dxf>
     <dxf>
       <font>
@@ -9036,7 +9039,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{45F55B1A-85F8-461D-BCBC-48B8D81FA567}" name="NotaDeVenta" displayName="NotaDeVenta" ref="B9:L110" totalsRowShown="0" headerRowDxfId="78" tableBorderDxfId="77">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{45F55B1A-85F8-461D-BCBC-48B8D81FA567}" name="NotaDeVenta" displayName="NotaDeVenta" ref="B9:L110" totalsRowShown="0" headerRowDxfId="74" tableBorderDxfId="73">
   <autoFilter ref="B9:L110" xr:uid="{45F55B1A-85F8-461D-BCBC-48B8D81FA567}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -9051,56 +9054,56 @@
     <filterColumn colId="10" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{717AD37F-47BA-4B3F-8D0E-A44EC339CC5E}" name="Producto" dataDxfId="76"/>
-    <tableColumn id="2" xr3:uid="{4503A827-7C13-4D61-9437-171D71ECD7E0}" name="Textil" dataDxfId="75"/>
-    <tableColumn id="3" xr3:uid="{C52B8C18-6CF8-4650-8EDE-E952978BA767}" name="Ancho Tela" dataDxfId="74">
+    <tableColumn id="1" xr3:uid="{717AD37F-47BA-4B3F-8D0E-A44EC339CC5E}" name="Producto" dataDxfId="72"/>
+    <tableColumn id="2" xr3:uid="{4503A827-7C13-4D61-9437-171D71ECD7E0}" name="Textil" dataDxfId="71"/>
+    <tableColumn id="3" xr3:uid="{C52B8C18-6CF8-4650-8EDE-E952978BA767}" name="Ancho Tela" dataDxfId="70">
       <calculatedColumnFormula>IF(ISTEXT(C10),VLOOKUP(C10,$AC$5:$AE$234,2,FALSE),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{03AF02AC-F147-40E6-837E-3A7C68289364}" name="Ancho" dataDxfId="73"/>
-    <tableColumn id="5" xr3:uid="{BEDF7098-F75C-4503-B040-7FADDCF45E44}" name="Alto" dataDxfId="72"/>
-    <tableColumn id="6" xr3:uid="{508B56CC-7A9D-4C53-AA08-E45FB037CFD5}" name="Cantidad" dataDxfId="71"/>
-    <tableColumn id="7" xr3:uid="{12518FAD-5240-4FBC-97E6-457FA2BD3150}" name="unid x ancho" dataDxfId="70">
+    <tableColumn id="4" xr3:uid="{03AF02AC-F147-40E6-837E-3A7C68289364}" name="Ancho" dataDxfId="69"/>
+    <tableColumn id="5" xr3:uid="{BEDF7098-F75C-4503-B040-7FADDCF45E44}" name="Alto" dataDxfId="68"/>
+    <tableColumn id="6" xr3:uid="{508B56CC-7A9D-4C53-AA08-E45FB037CFD5}" name="Cantidad" dataDxfId="67"/>
+    <tableColumn id="7" xr3:uid="{12518FAD-5240-4FBC-97E6-457FA2BD3150}" name="unid x ancho" dataDxfId="66">
       <calculatedColumnFormula>IF(ISNUMBER(E10),IF(ROUNDDOWN(D10/E10,0)&lt;1,NotaDeVenta[[#This Row],[Ancho Tela]]/NotaDeVenta[[#This Row],[Ancho]],ROUND(NotaDeVenta[[#This Row],[Ancho Tela]]/NotaDeVenta[[#This Row],[Ancho]],0)),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{8C168341-B116-4117-88CC-0EDBA4C99563}" name="ratio" dataDxfId="69">
+    <tableColumn id="8" xr3:uid="{8C168341-B116-4117-88CC-0EDBA4C99563}" name="ratio" dataDxfId="65">
       <calculatedColumnFormula>IF(ISNUMBER(H10),G10/H10,"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{E8EB34EB-C08D-47C3-A2EC-8CA8F96C8B49}" name="ML impresos" dataDxfId="68">
+    <tableColumn id="9" xr3:uid="{E8EB34EB-C08D-47C3-A2EC-8CA8F96C8B49}" name="ML impresos" dataDxfId="64">
       <calculatedColumnFormula>IF(ISNUMBER(G10),IF(OR(B10="Textil Backlight",B10="Caja + Backlight"),E10*F10*G10,F10*I10),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{3518F83C-159A-429E-9F69-E5DFA145C21A}" name="valor x ML" dataDxfId="67" dataCellStyle="Moneda">
+    <tableColumn id="10" xr3:uid="{3518F83C-159A-429E-9F69-E5DFA145C21A}" name="valor x ML" dataDxfId="63" dataCellStyle="Moneda">
       <calculatedColumnFormula>IF(ISTEXT(C10),VLOOKUP(C10,$AC$5:$AE$234,3,FALSE),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{199B2223-1634-4B59-8824-C8B2FA5A1957}" name="Tema" dataDxfId="66"/>
+    <tableColumn id="11" xr3:uid="{199B2223-1634-4B59-8824-C8B2FA5A1957}" name="Tema" dataDxfId="62"/>
   </tableColumns>
   <tableStyleInfo name="Estilo de tabla 1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{FCEAAFEB-A2CB-46CE-A1E3-B6D7E58B308F}" name="TablaValoresProducto" displayName="TablaValoresProducto" ref="B116:I216" totalsRowShown="0" headerRowDxfId="65" dataDxfId="63" headerRowBorderDxfId="64" tableBorderDxfId="62" dataCellStyle="Moneda">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{FCEAAFEB-A2CB-46CE-A1E3-B6D7E58B308F}" name="TablaValoresProducto" displayName="TablaValoresProducto" ref="B116:I216" totalsRowShown="0" headerRowDxfId="61" dataDxfId="59" headerRowBorderDxfId="60" tableBorderDxfId="58" dataCellStyle="Moneda">
   <autoFilter ref="B116:I216" xr:uid="{FCEAAFEB-A2CB-46CE-A1E3-B6D7E58B308F}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{56917B73-4D90-4EA1-9077-E5311434D134}" name="Producto" dataDxfId="61">
+    <tableColumn id="1" xr3:uid="{56917B73-4D90-4EA1-9077-E5311434D134}" name="Producto" dataDxfId="57">
       <calculatedColumnFormula>B10</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{7590FD35-5CAD-4465-95FD-DCCB224CF381}" name="Valor impresion total" dataDxfId="60" dataCellStyle="Moneda">
+    <tableColumn id="2" xr3:uid="{7590FD35-5CAD-4465-95FD-DCCB224CF381}" name="Valor impresion total" dataDxfId="56" dataCellStyle="Moneda">
       <calculatedColumnFormula>IF(ISNUMBER(K10),J10*K10,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{A5CF9EE5-D432-4A9C-AB66-BE05751BBAAA}" name="Estructura" dataDxfId="59" dataCellStyle="Moneda">
+    <tableColumn id="3" xr3:uid="{A5CF9EE5-D432-4A9C-AB66-BE05751BBAAA}" name="Estructura" dataDxfId="55" dataCellStyle="Moneda">
       <calculatedColumnFormula>IF(ISNUMBER(C117),VLOOKUP(B117,Productos!$A$2:$G$111,7,FALSE),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{D0A605E6-AD95-4778-9E19-3522DA6AB4D3}" name="Terminaciones" dataDxfId="58" dataCellStyle="Moneda">
+    <tableColumn id="4" xr3:uid="{D0A605E6-AD95-4778-9E19-3522DA6AB4D3}" name="Terminaciones" dataDxfId="54" dataCellStyle="Moneda">
       <calculatedColumnFormula>IF(B117&lt;&gt;"",VLOOKUP(B117,Productos!$A$2:$G$116,6,FALSE),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{1265221F-9861-480E-9924-B7A413822E57}" name="Otros x1" dataDxfId="57" dataCellStyle="Moneda"/>
-    <tableColumn id="6" xr3:uid="{6717EEF3-EF34-4B91-A2FC-CE0C4689C38E}" name="Valor unitario prod" dataDxfId="56" dataCellStyle="Moneda">
+    <tableColumn id="5" xr3:uid="{1265221F-9861-480E-9924-B7A413822E57}" name="Otros x1" dataDxfId="53" dataCellStyle="Moneda"/>
+    <tableColumn id="6" xr3:uid="{6717EEF3-EF34-4B91-A2FC-CE0C4689C38E}" name="Valor unitario prod" dataDxfId="52" dataCellStyle="Moneda">
       <calculatedColumnFormula>IF(B117="Caja + Backlight",'NV CAJAS (BL)'!L27+TablaValoresProducto[[#This Row],[Valor Impresión Unit]]+TablaValoresProducto[[#This Row],[Estructura]]+TablaValoresProducto[[#This Row],[Terminaciones]]+TablaValoresProducto[[#This Row],[Otros x1]],IF(ISNUMBER(TablaValoresProducto[[#This Row],[Valor impresion total]]),TablaValoresProducto[[#This Row],[Valor impresion total]]/G10+TablaValoresProducto[[#This Row],[Estructura]]+TablaValoresProducto[[#This Row],[Terminaciones]]+TablaValoresProducto[[#This Row],[Otros x1]],0))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{569040D7-FC75-49C0-8787-55BF059E5D99}" name="Total neto" dataDxfId="55" dataCellStyle="Moneda">
+    <tableColumn id="7" xr3:uid="{569040D7-FC75-49C0-8787-55BF059E5D99}" name="Total neto" dataDxfId="51" dataCellStyle="Moneda">
       <calculatedColumnFormula>IF(ISNUMBER(G117),G117*G10,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{37998E99-23E4-4828-AA9A-67968E1A29E1}" name="Valor Impresión Unit" dataDxfId="54" dataCellStyle="Moneda">
+    <tableColumn id="8" xr3:uid="{37998E99-23E4-4828-AA9A-67968E1A29E1}" name="Valor Impresión Unit" dataDxfId="50" dataCellStyle="Moneda">
       <calculatedColumnFormula>TablaValoresProducto[[#This Row],[Valor impresion total]]/G10</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9109,30 +9112,30 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{7B657EC5-7F3B-9F4F-981F-236A24BB6284}" name="COTIZACION" displayName="COTIZACION" ref="B11:I111" totalsRowShown="0" headerRowDxfId="90" headerRowBorderDxfId="89" tableBorderDxfId="88" totalsRowBorderDxfId="87">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{7B657EC5-7F3B-9F4F-981F-236A24BB6284}" name="COTIZACION" displayName="COTIZACION" ref="B11:I111" totalsRowShown="0" headerRowDxfId="49" headerRowBorderDxfId="48" tableBorderDxfId="47" totalsRowBorderDxfId="46">
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{4745F664-B0B9-8542-9C1F-99DB4E6D99D8}" name="Tema" dataDxfId="86">
+    <tableColumn id="1" xr3:uid="{4745F664-B0B9-8542-9C1F-99DB4E6D99D8}" name="Tema" dataDxfId="45">
       <calculatedColumnFormula>'Nota de venta'!L10</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{66BA370D-6B74-3747-9307-896EDEA400D0}" name="#" dataDxfId="85">
+    <tableColumn id="2" xr3:uid="{66BA370D-6B74-3747-9307-896EDEA400D0}" name="#" dataDxfId="44">
       <calculatedColumnFormula>'Nota de venta'!G10</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{2EF6C038-EA06-0143-B1EC-87AB369E2275}" name="Producto" dataDxfId="84">
+    <tableColumn id="3" xr3:uid="{2EF6C038-EA06-0143-B1EC-87AB369E2275}" name="Producto" dataDxfId="43">
       <calculatedColumnFormula>'Nota de venta'!B10</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{A5037E39-0905-4E4F-B60F-55DB643D6DC1}" name="Ancho" dataDxfId="83">
+    <tableColumn id="4" xr3:uid="{A5037E39-0905-4E4F-B60F-55DB643D6DC1}" name="Ancho" dataDxfId="42">
       <calculatedColumnFormula>'Nota de venta'!E10</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{6EA3C8C9-83E9-0042-9D1E-887391611AD8}" name="Alto" dataDxfId="82">
+    <tableColumn id="5" xr3:uid="{6EA3C8C9-83E9-0042-9D1E-887391611AD8}" name="Alto" dataDxfId="41">
       <calculatedColumnFormula>'Nota de venta'!F10</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{291314EE-E84A-4DE1-B4C8-D3F3F1B64B46}" name="ML" dataDxfId="81">
+    <tableColumn id="7" xr3:uid="{291314EE-E84A-4DE1-B4C8-D3F3F1B64B46}" name="ML" dataDxfId="40">
       <calculatedColumnFormula>'Nota de venta'!J10</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{DD337221-E570-134B-8506-169D19FC1775}" name="valor unitario" dataDxfId="80" dataCellStyle="Moneda">
+    <tableColumn id="6" xr3:uid="{DD337221-E570-134B-8506-169D19FC1775}" name="valor unitario" dataDxfId="39" dataCellStyle="Moneda">
       <calculatedColumnFormula>'Nota de venta'!G117</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{021C8C5C-A5B9-E34C-B161-FB4AA6331ACD}" name="Valor Total" dataDxfId="79" dataCellStyle="Moneda">
+    <tableColumn id="9" xr3:uid="{021C8C5C-A5B9-E34C-B161-FB4AA6331ACD}" name="Valor Total" dataDxfId="38" dataCellStyle="Moneda">
       <calculatedColumnFormula>IF(ISNUMBER(COTIZACION[[#This Row],[valor unitario]]),COTIZACION[[#This Row],[valor unitario]]*COTIZACION[[#This Row],['#]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9141,7 +9144,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{ED80DAF8-519B-4A4D-B992-A93E9E8C7AFD}" name="Tabla5" displayName="Tabla5" ref="A9:G110" totalsRowShown="0" headerRowDxfId="53" dataDxfId="51" headerRowBorderDxfId="52" tableBorderDxfId="50">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{ED80DAF8-519B-4A4D-B992-A93E9E8C7AFD}" name="Tabla5" displayName="Tabla5" ref="A9:G110" totalsRowShown="0" headerRowDxfId="37" dataDxfId="35" headerRowBorderDxfId="36" tableBorderDxfId="34">
   <autoFilter ref="A9:G110" xr:uid="{ED80DAF8-519B-4A4D-B992-A93E9E8C7AFD}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -9152,25 +9155,25 @@
     <filterColumn colId="6" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{47FE6556-6CF8-4AFE-88B5-72DFBBA14078}" name="TEMA" dataDxfId="49">
+    <tableColumn id="1" xr3:uid="{47FE6556-6CF8-4AFE-88B5-72DFBBA14078}" name="TEMA" dataDxfId="33">
       <calculatedColumnFormula>NotaDeVenta[[#This Row],[Tema]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{525375BC-4E2E-496E-B4F9-08B3FBEEF9B1}" name="Producto" dataDxfId="48">
+    <tableColumn id="2" xr3:uid="{525375BC-4E2E-496E-B4F9-08B3FBEEF9B1}" name="Producto" dataDxfId="32">
       <calculatedColumnFormula>NotaDeVenta[[#This Row],[Producto]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{3CE00620-917F-4A12-BA27-646A12893A66}" name="Textil" dataDxfId="47">
+    <tableColumn id="3" xr3:uid="{3CE00620-917F-4A12-BA27-646A12893A66}" name="Textil" dataDxfId="31">
       <calculatedColumnFormula>NotaDeVenta[[#This Row],[Textil]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{472F8946-F36B-413D-81C6-1AC9FE8DC79D}" name="Ancho" dataDxfId="46">
+    <tableColumn id="4" xr3:uid="{472F8946-F36B-413D-81C6-1AC9FE8DC79D}" name="Ancho" dataDxfId="30">
       <calculatedColumnFormula>NotaDeVenta[[#This Row],[Ancho]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{4E38C9D9-DDB3-4F1B-BD73-1FFDD0F162A9}" name="Alto" dataDxfId="45">
+    <tableColumn id="5" xr3:uid="{4E38C9D9-DDB3-4F1B-BD73-1FFDD0F162A9}" name="Alto" dataDxfId="29">
       <calculatedColumnFormula>NotaDeVenta[[#This Row],[Alto]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{0F400A98-CF2F-4A66-9073-BF80B6A6E8EB}" name="#" dataDxfId="44">
+    <tableColumn id="6" xr3:uid="{0F400A98-CF2F-4A66-9073-BF80B6A6E8EB}" name="#" dataDxfId="28">
       <calculatedColumnFormula>NotaDeVenta[[#This Row],[Cantidad]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{602737AF-275E-4BB3-9EF9-0CD1DACBC55F}" name="ML" dataDxfId="43">
+    <tableColumn id="7" xr3:uid="{602737AF-275E-4BB3-9EF9-0CD1DACBC55F}" name="ML" dataDxfId="27">
       <calculatedColumnFormula>NotaDeVenta[[#This Row],[ML impresos]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9179,44 +9182,44 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{25525FA2-F71E-0047-86C1-963F31BDB788}" name="TablaOpTelas" displayName="TablaOpTelas" ref="B8:N108" totalsRowShown="0" headerRowDxfId="42" dataDxfId="41" tableBorderDxfId="40">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{25525FA2-F71E-0047-86C1-963F31BDB788}" name="TablaOpTelas" displayName="TablaOpTelas" ref="B8:N108" totalsRowShown="0" headerRowDxfId="90" dataDxfId="89" tableBorderDxfId="88">
   <autoFilter ref="B8:N108" xr:uid="{25525FA2-F71E-0047-86C1-963F31BDB788}"/>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{525B3110-BCC1-1949-8797-1E5E79B63D5B}" name="textil" dataDxfId="39">
+    <tableColumn id="1" xr3:uid="{525B3110-BCC1-1949-8797-1E5E79B63D5B}" name="textil" dataDxfId="87">
       <calculatedColumnFormula>'Nota de venta'!C10</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{3254CD78-FAEF-7C47-9511-61E1E2F9D434}" name="#" dataDxfId="38">
+    <tableColumn id="2" xr3:uid="{3254CD78-FAEF-7C47-9511-61E1E2F9D434}" name="#" dataDxfId="86">
       <calculatedColumnFormula>'Nota de venta'!G10</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{4D2727CE-1D91-9E40-AEAE-40136A814E26}" name="ANCHO" dataDxfId="37">
+    <tableColumn id="3" xr3:uid="{4D2727CE-1D91-9E40-AEAE-40136A814E26}" name="ANCHO" dataDxfId="85">
       <calculatedColumnFormula>'Nota de venta'!E10</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{4CE97519-CB9A-D647-9E76-540CF01B2C51}" name="ALTO" dataDxfId="36">
+    <tableColumn id="4" xr3:uid="{4CE97519-CB9A-D647-9E76-540CF01B2C51}" name="ALTO" dataDxfId="84">
       <calculatedColumnFormula>'Nota de venta'!F10</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{FB3711BA-F0FC-CE42-A723-BCD1110A9FA5}" name="exc cms x lado" dataDxfId="35"/>
-    <tableColumn id="6" xr3:uid="{522BE264-EE7F-9B40-991A-CFBBE4FEC689}" name="ancho final" dataDxfId="34">
+    <tableColumn id="5" xr3:uid="{FB3711BA-F0FC-CE42-A723-BCD1110A9FA5}" name="exc cms x lado" dataDxfId="83"/>
+    <tableColumn id="6" xr3:uid="{522BE264-EE7F-9B40-991A-CFBBE4FEC689}" name="ancho final" dataDxfId="82">
       <calculatedColumnFormula>TablaOpTelas[[#This Row],[ANCHO]]+(TablaOpTelas[[#This Row],[exc cms x lado]]/100)*2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{2EDA380A-5DE1-F348-857A-E7AA5BAD9472}" name="alto final" dataDxfId="33">
+    <tableColumn id="7" xr3:uid="{2EDA380A-5DE1-F348-857A-E7AA5BAD9472}" name="alto final" dataDxfId="81">
       <calculatedColumnFormula>TablaOpTelas[[#This Row],[ALTO]]+(TablaOpTelas[[#This Row],[exc cms x lado]]/100)*2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{6943F06A-6C66-6D41-BFC2-960182ED4796}" name="m2 unit" dataDxfId="32">
+    <tableColumn id="8" xr3:uid="{6943F06A-6C66-6D41-BFC2-960182ED4796}" name="m2 unit" dataDxfId="80">
       <calculatedColumnFormula>TablaOpTelas[[#This Row],[ancho final]]*TablaOpTelas[[#This Row],[alto final]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{F705AC6B-8DEC-5F44-9B72-BEFA6886DB7B}" name="m2 total" dataDxfId="31">
+    <tableColumn id="9" xr3:uid="{F705AC6B-8DEC-5F44-9B72-BEFA6886DB7B}" name="m2 total" dataDxfId="79">
       <calculatedColumnFormula>TablaOpTelas[[#This Row],[m2 unit]]*TablaOpTelas[[#This Row],['#]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{E4FCF294-22D3-B046-B2E3-B9344BC57156}" name="valor unit" dataDxfId="30">
+    <tableColumn id="10" xr3:uid="{E4FCF294-22D3-B046-B2E3-B9344BC57156}" name="valor unit" dataDxfId="78">
       <calculatedColumnFormula>TablaOpTelas[[#This Row],[ANCHO]]*TablaOpTelas[[#This Row],[ALTO]]*$J$6</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{D00DD6C0-4E70-674B-A603-7858D738D1ED}" name="corte ancho" dataDxfId="29">
+    <tableColumn id="11" xr3:uid="{D00DD6C0-4E70-674B-A603-7858D738D1ED}" name="corte ancho" dataDxfId="77">
       <calculatedColumnFormula>IF($J$7="CAJA TERMINADA",TablaOpTelas[[#This Row],[ANCHO]]+0.013,TablaOpTelas[[#This Row],[ANCHO]]+0.023)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{572DC0C8-0A78-BE46-AF1C-C74F523B793A}" name="corte alto" dataDxfId="28">
+    <tableColumn id="12" xr3:uid="{572DC0C8-0A78-BE46-AF1C-C74F523B793A}" name="corte alto" dataDxfId="76">
       <calculatedColumnFormula>IF($J$7="CAJA TERMINADA",TablaOpTelas[[#This Row],[ALTO]]+0.013,TablaOpTelas[[#This Row],[ALTO]]+0.023)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{F9206661-B6BF-394F-8A3C-037D45BE20AB}" name="tema" dataDxfId="27">
+    <tableColumn id="13" xr3:uid="{F9206661-B6BF-394F-8A3C-037D45BE20AB}" name="tema" dataDxfId="75">
       <calculatedColumnFormula>'Nota de venta'!L10</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9618,20 +9621,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" s="54" customFormat="1">
-      <c r="C1" s="504" t="s">
+      <c r="C1" s="511" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="506"/>
-      <c r="E1" s="505"/>
-      <c r="F1" s="504" t="s">
+      <c r="D1" s="513"/>
+      <c r="E1" s="512"/>
+      <c r="F1" s="511" t="s">
         <v>93</v>
       </c>
-      <c r="G1" s="506"/>
-      <c r="H1" s="505"/>
-      <c r="I1" s="504" t="s">
+      <c r="G1" s="513"/>
+      <c r="H1" s="512"/>
+      <c r="I1" s="511" t="s">
         <v>56</v>
       </c>
-      <c r="J1" s="505"/>
+      <c r="J1" s="512"/>
     </row>
     <row r="2" spans="1:10" s="54" customFormat="1">
       <c r="A2" s="55" t="s">
@@ -10043,54 +10046,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="5" customHeight="1">
-      <c r="H1" s="509"/>
-      <c r="I1" s="509"/>
+      <c r="H1" s="524"/>
+      <c r="I1" s="524"/>
     </row>
     <row r="2" spans="1:43" ht="22.9" customHeight="1">
       <c r="B2" s="324" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C2" s="394"/>
       <c r="G2" s="324" t="s">
-        <v>397</v>
-      </c>
-      <c r="H2" s="509"/>
-      <c r="I2" s="509"/>
+        <v>396</v>
+      </c>
+      <c r="H2" s="524"/>
+      <c r="I2" s="524"/>
       <c r="Z2" s="323" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="3" spans="1:43" ht="5" customHeight="1">
-      <c r="H3" s="509"/>
-      <c r="I3" s="509"/>
+      <c r="H3" s="524"/>
+      <c r="I3" s="524"/>
     </row>
     <row r="4" spans="1:43" ht="14.25">
-      <c r="B4" s="507" t="s">
+      <c r="B4" s="522" t="s">
         <v>45</v>
       </c>
-      <c r="C4" s="508"/>
-      <c r="D4" s="508"/>
-      <c r="E4" s="508"/>
-      <c r="F4" s="508"/>
-      <c r="G4" s="508"/>
-      <c r="H4" s="508"/>
-      <c r="I4" s="508"/>
-      <c r="J4" s="508"/>
+      <c r="C4" s="523"/>
+      <c r="D4" s="523"/>
+      <c r="E4" s="523"/>
+      <c r="F4" s="523"/>
+      <c r="G4" s="523"/>
+      <c r="H4" s="523"/>
+      <c r="I4" s="523"/>
+      <c r="J4" s="523"/>
       <c r="Z4" s="325" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="AA4" s="325"/>
       <c r="AC4" s="325" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="AD4" s="325" t="s">
         <v>298</v>
       </c>
       <c r="AE4" s="325" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AG4" s="335" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AH4" s="336">
         <v>0.1</v>
@@ -10099,35 +10102,35 @@
         <v>72</v>
       </c>
       <c r="AK4" s="351" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AQ4" s="323" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="5" spans="1:43" ht="17.350000000000001" customHeight="1">
       <c r="B5" s="324" t="s">
         <v>55</v>
       </c>
-      <c r="C5" s="510"/>
-      <c r="D5" s="510"/>
-      <c r="E5" s="510"/>
-      <c r="F5" s="510"/>
-      <c r="G5" s="510"/>
+      <c r="C5" s="518"/>
+      <c r="D5" s="518"/>
+      <c r="E5" s="518"/>
+      <c r="F5" s="518"/>
+      <c r="G5" s="518"/>
       <c r="H5" s="324" t="s">
-        <v>398</v>
-      </c>
-      <c r="I5" s="512"/>
-      <c r="J5" s="512"/>
-      <c r="K5" s="512"/>
-      <c r="L5" s="512"/>
+        <v>397</v>
+      </c>
+      <c r="I5" s="519"/>
+      <c r="J5" s="519"/>
+      <c r="K5" s="519"/>
+      <c r="L5" s="519"/>
       <c r="Z5" s="328" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AA5"/>
       <c r="AB5"/>
       <c r="AC5" s="337" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="AD5" s="338">
         <v>1.53</v>
@@ -10136,36 +10139,36 @@
         <v>27000</v>
       </c>
       <c r="AJ5" s="125" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AK5" s="352">
         <v>7500</v>
       </c>
       <c r="AQ5" s="323" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="6" spans="1:43" ht="17.350000000000001" customHeight="1">
       <c r="B6" s="324" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="512"/>
-      <c r="D6" s="512"/>
-      <c r="E6" s="512"/>
-      <c r="F6" s="512"/>
-      <c r="G6" s="512"/>
+      <c r="C6" s="519"/>
+      <c r="D6" s="519"/>
+      <c r="E6" s="519"/>
+      <c r="F6" s="519"/>
+      <c r="G6" s="519"/>
       <c r="H6" s="324" t="s">
-        <v>337</v>
-      </c>
-      <c r="I6" s="510"/>
-      <c r="J6" s="510"/>
+        <v>336</v>
+      </c>
+      <c r="I6" s="518"/>
+      <c r="J6" s="518"/>
       <c r="Z6" s="328" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="AA6"/>
       <c r="AB6"/>
       <c r="AC6" s="340" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="AD6" s="341">
         <v>3.08</v>
@@ -10174,36 +10177,36 @@
         <v>31000</v>
       </c>
       <c r="AJ6" s="125" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="AK6" s="352">
         <v>17000</v>
       </c>
       <c r="AQ6" s="323" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="7" spans="1:43" ht="17.350000000000001" customHeight="1">
       <c r="B7" s="324" t="s">
-        <v>339</v>
-      </c>
-      <c r="C7" s="512"/>
-      <c r="D7" s="512"/>
-      <c r="E7" s="512"/>
-      <c r="F7" s="512"/>
-      <c r="G7" s="512"/>
+        <v>338</v>
+      </c>
+      <c r="C7" s="519"/>
+      <c r="D7" s="519"/>
+      <c r="E7" s="519"/>
+      <c r="F7" s="519"/>
+      <c r="G7" s="519"/>
       <c r="H7" s="324" t="s">
         <v>5</v>
       </c>
-      <c r="I7" s="511"/>
-      <c r="J7" s="511"/>
+      <c r="I7" s="525"/>
+      <c r="J7" s="525"/>
       <c r="Z7" s="329" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="AA7" s="107"/>
       <c r="AB7" s="107"/>
       <c r="AC7" s="343" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="AD7" s="344">
         <v>1.53</v>
@@ -10212,23 +10215,23 @@
         <v>23000</v>
       </c>
       <c r="AJ7" s="124" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="AK7" s="352">
         <v>19000</v>
       </c>
       <c r="AQ7" s="323" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="8" spans="1:43" ht="17.649999999999999" customHeight="1">
       <c r="Z8" s="328" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="AA8"/>
       <c r="AB8"/>
       <c r="AC8" s="340" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="AD8" s="341">
         <v>3.08</v>
@@ -10237,13 +10240,13 @@
         <v>31000</v>
       </c>
       <c r="AJ8" s="125" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="AK8" s="353">
         <v>5000</v>
       </c>
       <c r="AQ8" s="323" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9" spans="1:43" ht="23.65" customHeight="1">
@@ -10251,10 +10254,10 @@
         <v>72</v>
       </c>
       <c r="C9" s="444" t="s">
+        <v>339</v>
+      </c>
+      <c r="D9" s="444" t="s">
         <v>340</v>
-      </c>
-      <c r="D9" s="444" t="s">
-        <v>341</v>
       </c>
       <c r="E9" s="444" t="s">
         <v>298</v>
@@ -10266,27 +10269,27 @@
         <v>6</v>
       </c>
       <c r="H9" s="444" t="s">
+        <v>341</v>
+      </c>
+      <c r="I9" s="444" t="s">
         <v>342</v>
       </c>
-      <c r="I9" s="444" t="s">
+      <c r="J9" s="444" t="s">
         <v>343</v>
       </c>
-      <c r="J9" s="444" t="s">
-        <v>344</v>
-      </c>
       <c r="K9" s="444" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="L9" s="444" t="s">
         <v>229</v>
       </c>
       <c r="Z9" s="330" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="AA9" s="334"/>
       <c r="AB9" s="334"/>
       <c r="AC9" s="346" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="AD9" s="347">
         <v>1.6</v>
@@ -10295,13 +10298,13 @@
         <v>23000</v>
       </c>
       <c r="AJ9" s="152" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="AK9" s="352">
         <v>11000</v>
       </c>
       <c r="AQ9" s="323" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="10" spans="1:43" ht="15.75">
@@ -10338,12 +10341,12 @@
       </c>
       <c r="M10" s="396"/>
       <c r="Z10" s="331" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AA10" s="177"/>
       <c r="AB10" s="177"/>
       <c r="AC10" s="271" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="AD10" s="125">
         <v>1.48</v>
@@ -10352,13 +10355,13 @@
         <v>11000</v>
       </c>
       <c r="AJ10" s="326" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AK10" s="352">
         <v>15000</v>
       </c>
       <c r="AQ10" s="323" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="11" spans="1:43" ht="15.75">
@@ -14072,12 +14075,12 @@
       </c>
       <c r="L103" s="429"/>
       <c r="Z103" s="328" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AA103"/>
       <c r="AB103"/>
       <c r="AC103" s="272" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="AD103" s="124">
         <v>1.48</v>
@@ -14086,13 +14089,13 @@
         <v>12000</v>
       </c>
       <c r="AJ103" s="125" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AK103" s="352">
         <v>25000</v>
       </c>
       <c r="AQ103" s="323" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="104" spans="1:43" ht="15.75">
@@ -14126,12 +14129,12 @@
       </c>
       <c r="L104" s="429"/>
       <c r="Z104" s="328" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="AA104"/>
       <c r="AB104"/>
       <c r="AC104" s="271" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="AD104" s="125">
         <v>1.48</v>
@@ -14140,13 +14143,13 @@
         <v>11000</v>
       </c>
       <c r="AJ104" s="125" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="AK104" s="352">
         <v>5000</v>
       </c>
       <c r="AQ104" s="323" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="105" spans="1:43" ht="15.75">
@@ -14180,12 +14183,12 @@
       </c>
       <c r="L105" s="429"/>
       <c r="Z105" s="328" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="AA105"/>
       <c r="AB105"/>
       <c r="AC105" s="272" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="AD105" s="124">
         <v>1.48</v>
@@ -14194,13 +14197,13 @@
         <v>11000</v>
       </c>
       <c r="AJ105" s="125" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="AK105" s="352">
         <v>3500</v>
       </c>
       <c r="AQ105" s="323" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="106" spans="1:43" ht="15.75">
@@ -14234,12 +14237,12 @@
       </c>
       <c r="L106" s="429"/>
       <c r="Z106" s="330" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AA106" s="334"/>
       <c r="AB106" s="334"/>
       <c r="AC106" s="272" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="AD106" s="124">
         <v>1.38</v>
@@ -14248,13 +14251,13 @@
         <v>10000</v>
       </c>
       <c r="AJ106" s="152" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AK106" s="352">
         <v>10000</v>
       </c>
       <c r="AQ106" s="323" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="107" spans="1:43" ht="15.75">
@@ -14288,12 +14291,12 @@
       </c>
       <c r="L107" s="429"/>
       <c r="Z107" s="328" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AA107"/>
       <c r="AB107"/>
       <c r="AC107" s="271" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="AD107" s="125">
         <v>1.38</v>
@@ -14302,13 +14305,13 @@
         <v>12000</v>
       </c>
       <c r="AJ107" s="125" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AK107" s="352">
         <v>2000</v>
       </c>
       <c r="AQ107" s="323" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="108" spans="1:43" ht="15.75">
@@ -14420,12 +14423,12 @@
       </c>
       <c r="L110" s="443"/>
       <c r="Z110" s="328" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AA110"/>
       <c r="AB110"/>
       <c r="AC110" s="271" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="AD110" s="125">
         <v>1.38</v>
@@ -14434,13 +14437,13 @@
         <v>12000</v>
       </c>
       <c r="AJ110" s="125" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AK110" s="352">
         <v>3000</v>
       </c>
       <c r="AQ110" s="323" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="111" spans="1:43" ht="16.149999999999999" thickBot="1">
@@ -14457,12 +14460,12 @@
         <v>0</v>
       </c>
       <c r="Z111" s="328" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AA111"/>
       <c r="AB111"/>
       <c r="AC111" s="272" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="AD111" s="124">
         <v>1.48</v>
@@ -14471,27 +14474,27 @@
         <v>12000</v>
       </c>
       <c r="AJ111" s="125" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AK111" s="352">
         <v>10500</v>
       </c>
       <c r="AQ111" s="323" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="112" spans="1:43" ht="30" customHeight="1" thickBot="1">
       <c r="B112" s="349" t="s">
-        <v>620</v>
-      </c>
-      <c r="C112" s="517"/>
-      <c r="D112" s="517"/>
-      <c r="E112" s="517"/>
-      <c r="F112" s="517"/>
-      <c r="G112" s="517"/>
-      <c r="H112" s="517"/>
-      <c r="I112" s="517"/>
-      <c r="J112" s="518"/>
+        <v>619</v>
+      </c>
+      <c r="C112" s="520"/>
+      <c r="D112" s="520"/>
+      <c r="E112" s="520"/>
+      <c r="F112" s="520"/>
+      <c r="G112" s="520"/>
+      <c r="H112" s="520"/>
+      <c r="I112" s="520"/>
+      <c r="J112" s="521"/>
       <c r="Z112" s="328"/>
       <c r="AA112"/>
       <c r="AB112"/>
@@ -14503,23 +14506,23 @@
     </row>
     <row r="113" spans="1:43" ht="30" customHeight="1" thickBot="1">
       <c r="B113" s="349" t="s">
-        <v>387</v>
-      </c>
-      <c r="C113" s="513"/>
-      <c r="D113" s="513"/>
-      <c r="E113" s="513"/>
-      <c r="F113" s="513"/>
-      <c r="G113" s="513"/>
-      <c r="H113" s="513"/>
-      <c r="I113" s="513"/>
-      <c r="J113" s="514"/>
+        <v>386</v>
+      </c>
+      <c r="C113" s="514"/>
+      <c r="D113" s="514"/>
+      <c r="E113" s="514"/>
+      <c r="F113" s="514"/>
+      <c r="G113" s="514"/>
+      <c r="H113" s="514"/>
+      <c r="I113" s="514"/>
+      <c r="J113" s="515"/>
       <c r="Z113" s="328" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AA113"/>
       <c r="AB113"/>
       <c r="AC113" s="272" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="AD113" s="124">
         <v>1.48</v>
@@ -14528,34 +14531,34 @@
         <v>12000</v>
       </c>
       <c r="AJ113" s="125" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AK113" s="352">
         <v>6000</v>
       </c>
       <c r="AQ113" s="323" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="114" spans="1:43" ht="30" customHeight="1" thickBot="1">
       <c r="B114" s="350" t="s">
-        <v>388</v>
-      </c>
-      <c r="C114" s="515"/>
-      <c r="D114" s="515"/>
-      <c r="E114" s="515"/>
-      <c r="F114" s="515"/>
-      <c r="G114" s="515"/>
-      <c r="H114" s="515"/>
-      <c r="I114" s="515"/>
-      <c r="J114" s="516"/>
+        <v>387</v>
+      </c>
+      <c r="C114" s="516"/>
+      <c r="D114" s="516"/>
+      <c r="E114" s="516"/>
+      <c r="F114" s="516"/>
+      <c r="G114" s="516"/>
+      <c r="H114" s="516"/>
+      <c r="I114" s="516"/>
+      <c r="J114" s="517"/>
       <c r="Z114" s="329" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AA114" s="107"/>
       <c r="AB114" s="107"/>
       <c r="AC114" s="271" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="AD114" s="125">
         <v>1.46</v>
@@ -14564,25 +14567,25 @@
         <v>12000</v>
       </c>
       <c r="AJ114" s="124" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AK114" s="352">
         <v>4000</v>
       </c>
       <c r="AQ114" s="323" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="115" spans="1:43" ht="15.75">
       <c r="B115" s="357"/>
       <c r="I115" s="356"/>
       <c r="Z115" s="328" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="AA115"/>
       <c r="AB115"/>
       <c r="AC115" s="271" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="AD115" s="125">
         <v>1.38</v>
@@ -14591,13 +14594,13 @@
         <v>12800</v>
       </c>
       <c r="AJ115" s="125" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="AK115" s="352">
         <v>7000</v>
       </c>
       <c r="AQ115" s="323" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="116" spans="1:43" ht="28.9" thickBot="1">
@@ -14605,33 +14608,33 @@
         <v>72</v>
       </c>
       <c r="C116" s="450" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="D116" s="450" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E116" s="450" t="s">
         <v>125</v>
       </c>
       <c r="F116" s="450" t="s">
+        <v>388</v>
+      </c>
+      <c r="G116" s="450" t="s">
         <v>389</v>
       </c>
-      <c r="G116" s="450" t="s">
+      <c r="H116" s="451" t="s">
         <v>390</v>
       </c>
-      <c r="H116" s="451" t="s">
-        <v>391</v>
-      </c>
       <c r="I116" s="450" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="Z116" s="329" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AA116" s="107"/>
       <c r="AB116" s="107"/>
       <c r="AC116" s="272" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="AD116" s="124">
         <v>1.58</v>
@@ -14640,13 +14643,13 @@
         <v>8000</v>
       </c>
       <c r="AJ116" s="124" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AK116" s="352">
         <v>10000</v>
       </c>
       <c r="AQ116" s="323" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="117" spans="1:43" ht="28.9" thickTop="1">
@@ -14683,12 +14686,12 @@
         <v>#DIV/0!</v>
       </c>
       <c r="Z117" s="330" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AA117" s="334"/>
       <c r="AB117" s="334"/>
       <c r="AC117" s="272" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="AD117" s="124">
         <v>1.48</v>
@@ -14697,13 +14700,13 @@
         <v>10500</v>
       </c>
       <c r="AJ117" s="152" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AK117" s="352">
         <v>15000</v>
       </c>
       <c r="AQ117" s="323" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="118" spans="1:43" ht="15.75">
@@ -18606,12 +18609,12 @@
         <v>#DIV/0!</v>
       </c>
       <c r="Z210" s="330" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AA210" s="334"/>
       <c r="AB210" s="334"/>
       <c r="AC210" s="271" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="AD210" s="125">
         <v>1.4</v>
@@ -18620,13 +18623,13 @@
         <v>11000</v>
       </c>
       <c r="AJ210" s="152" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AK210" s="352">
         <v>18000</v>
       </c>
       <c r="AQ210" s="323" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="211" spans="1:43" ht="15.75">
@@ -18665,12 +18668,12 @@
         <v>#DIV/0!</v>
       </c>
       <c r="Z211" s="328" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AA211"/>
       <c r="AB211"/>
       <c r="AC211" s="271" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="AD211" s="125">
         <v>1.38</v>
@@ -18679,13 +18682,13 @@
         <v>15000</v>
       </c>
       <c r="AJ211" s="125" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AK211" s="352">
         <v>4000</v>
       </c>
       <c r="AQ211" s="323" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="212" spans="1:43" ht="15.75">
@@ -18724,12 +18727,12 @@
         <v>#DIV/0!</v>
       </c>
       <c r="Z212" s="328" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AA212"/>
       <c r="AB212"/>
       <c r="AC212" s="271" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="AD212" s="125">
         <v>1.58</v>
@@ -18738,7 +18741,7 @@
         <v>12000</v>
       </c>
       <c r="AJ212" s="125" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AK212" s="352">
         <v>7000</v>
@@ -18750,7 +18753,7 @@
         <v>0</v>
       </c>
       <c r="AQ212" s="323" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="213" spans="1:43" ht="15.75">
@@ -18789,12 +18792,12 @@
         <v>#DIV/0!</v>
       </c>
       <c r="Z213" s="329" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AA213" s="107"/>
       <c r="AB213" s="107"/>
       <c r="AC213" s="271" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="AD213" s="125">
         <v>1.44</v>
@@ -18803,7 +18806,7 @@
         <v>13000</v>
       </c>
       <c r="AJ213" s="124" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AK213" s="352">
         <v>96000</v>
@@ -18815,7 +18818,7 @@
         <v>0</v>
       </c>
       <c r="AQ213" s="323" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="214" spans="1:43" ht="15.75">
@@ -18854,12 +18857,12 @@
         <v>#DIV/0!</v>
       </c>
       <c r="Z214" s="328" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AA214"/>
       <c r="AB214"/>
       <c r="AC214" s="272" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="AD214" s="124">
         <v>1.44</v>
@@ -18868,7 +18871,7 @@
         <v>12500</v>
       </c>
       <c r="AJ214" s="125" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AK214" s="354">
         <v>85000</v>
@@ -18880,7 +18883,7 @@
         <v>0.05</v>
       </c>
       <c r="AQ214" s="323" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="215" spans="1:43" ht="15.75">
@@ -18919,12 +18922,12 @@
         <v>#DIV/0!</v>
       </c>
       <c r="Z215" s="328" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AA215"/>
       <c r="AB215"/>
       <c r="AC215" s="272" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="AD215" s="124">
         <v>1.48</v>
@@ -18933,7 +18936,7 @@
         <v>12000</v>
       </c>
       <c r="AJ215" s="125" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AK215" s="354">
         <v>120000</v>
@@ -18945,7 +18948,7 @@
         <v>0.1</v>
       </c>
       <c r="AQ215" s="323" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="216" spans="1:43" ht="15.75">
@@ -18984,12 +18987,12 @@
         <v>#DIV/0!</v>
       </c>
       <c r="Z216" s="328" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="AA216"/>
       <c r="AB216"/>
       <c r="AC216" s="397" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="AD216" s="149">
         <v>1.44</v>
@@ -18998,7 +19001,7 @@
         <v>12600</v>
       </c>
       <c r="AJ216" s="125" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="AK216" s="354">
         <v>140000</v>
@@ -19010,17 +19013,17 @@
         <v>0.2</v>
       </c>
       <c r="AQ216" s="323" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="217" spans="1:43" ht="15" customHeight="1">
       <c r="Z217" s="330" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AA217" s="334"/>
       <c r="AB217" s="334"/>
       <c r="AC217" s="271" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="AD217" s="125">
         <v>1.48</v>
@@ -19029,7 +19032,7 @@
         <v>12500</v>
       </c>
       <c r="AJ217" s="152" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AK217" s="355">
         <v>170000</v>
@@ -19042,17 +19045,17 @@
         <v>0</v>
       </c>
       <c r="AQ217" s="323" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="218" spans="1:43" ht="15" customHeight="1">
       <c r="Z218" s="328" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="AA218"/>
       <c r="AB218"/>
       <c r="AC218" s="271" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="AD218" s="125">
         <v>1.48</v>
@@ -19061,23 +19064,23 @@
         <v>12300</v>
       </c>
       <c r="AJ218" s="125" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="AK218" s="354">
         <v>205000</v>
       </c>
       <c r="AQ218" s="323" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="219" spans="1:43" ht="15" customHeight="1">
       <c r="Z219" s="329" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AA219" s="107"/>
       <c r="AB219" s="107"/>
       <c r="AC219" s="398" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="AD219" s="327">
         <v>1.58</v>
@@ -19086,23 +19089,23 @@
         <v>16320</v>
       </c>
       <c r="AJ219" s="124" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AK219" s="355">
         <v>245000</v>
       </c>
       <c r="AQ219" s="323" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="220" spans="1:43" ht="15" customHeight="1">
       <c r="Z220" s="328" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AA220"/>
       <c r="AB220"/>
       <c r="AC220" s="272" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="AD220" s="124">
         <v>2.8</v>
@@ -19111,23 +19114,23 @@
         <v>30000</v>
       </c>
       <c r="AJ220" s="125" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AK220" s="352">
         <v>8000</v>
       </c>
       <c r="AQ220" s="323" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="221" spans="1:43" ht="15" customHeight="1">
       <c r="Z221" s="328" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="AA221"/>
       <c r="AB221"/>
       <c r="AC221" s="271" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="AD221" s="125">
         <v>1.58</v>
@@ -19136,23 +19139,23 @@
         <v>9600</v>
       </c>
       <c r="AJ221" s="125" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="AK221" s="352">
         <v>5000</v>
       </c>
       <c r="AQ221" s="323" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="222" spans="1:43" ht="15" customHeight="1">
       <c r="Z222" s="328" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="AA222"/>
       <c r="AB222"/>
       <c r="AC222" s="271" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="AD222" s="125">
         <v>1.1000000000000001</v>
@@ -19161,23 +19164,23 @@
         <v>12000</v>
       </c>
       <c r="AJ222" s="125" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="AK222" s="352">
         <v>4000</v>
       </c>
       <c r="AQ222" s="323" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="223" spans="1:43" ht="15" customHeight="1">
       <c r="Z223" s="328" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="AA223"/>
       <c r="AB223"/>
       <c r="AC223" s="272" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="AD223" s="124">
         <v>1.1000000000000001</v>
@@ -19186,23 +19189,23 @@
         <v>12000</v>
       </c>
       <c r="AJ223" s="125" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="AK223" s="352">
         <v>8000</v>
       </c>
       <c r="AQ223" s="323" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="224" spans="1:43" ht="15" customHeight="1">
       <c r="Z224" s="328" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AA224"/>
       <c r="AB224"/>
       <c r="AC224" s="272" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="AD224" s="124">
         <v>1.38</v>
@@ -19211,23 +19214,23 @@
         <v>11100</v>
       </c>
       <c r="AJ224" s="125" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AK224" s="352">
         <v>10000</v>
       </c>
       <c r="AQ224" s="323" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="225" spans="25:43" ht="15" customHeight="1">
       <c r="Z225" s="328" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AA225"/>
       <c r="AB225"/>
       <c r="AC225" s="272" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="AD225" s="124">
         <v>1.48</v>
@@ -19236,23 +19239,23 @@
         <v>11300</v>
       </c>
       <c r="AJ225" s="125" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AK225" s="352">
         <v>15000</v>
       </c>
       <c r="AQ225" s="323" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="226" spans="25:43" ht="15" customHeight="1">
       <c r="Z226" s="330" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AA226" s="334"/>
       <c r="AB226" s="334"/>
       <c r="AC226" s="271" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="AD226" s="125">
         <v>1.48</v>
@@ -19261,23 +19264,23 @@
         <v>10800</v>
       </c>
       <c r="AJ226" s="152" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AK226" s="352">
         <v>0</v>
       </c>
       <c r="AQ226" s="323" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="227" spans="25:43" ht="15" customHeight="1">
       <c r="Z227" s="328" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AA227"/>
       <c r="AB227"/>
       <c r="AC227" s="271" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="AD227" s="125">
         <v>2.2799999999999998</v>
@@ -19286,23 +19289,23 @@
         <v>27400</v>
       </c>
       <c r="AJ227" s="125" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AK227" s="352">
         <v>10000</v>
       </c>
       <c r="AQ227" s="323" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="228" spans="25:43" ht="15" customHeight="1">
       <c r="Z228" s="328" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="AA228"/>
       <c r="AB228"/>
       <c r="AC228" s="272" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="AD228" s="124">
         <v>1.48</v>
@@ -19311,23 +19314,23 @@
         <v>11000</v>
       </c>
       <c r="AJ228" s="125" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="AK228" s="353">
         <v>3000</v>
       </c>
       <c r="AQ228" s="323" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="229" spans="25:43" ht="15" customHeight="1">
       <c r="Z229" s="328" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AA229"/>
       <c r="AB229"/>
       <c r="AC229" s="271" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="AD229" s="125">
         <v>1.48</v>
@@ -19336,23 +19339,23 @@
         <v>10000</v>
       </c>
       <c r="AJ229" s="125" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AK229" s="352">
         <v>13000</v>
       </c>
       <c r="AQ229" s="323" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="230" spans="25:43" ht="15" customHeight="1">
       <c r="Z230" s="328" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AA230"/>
       <c r="AB230"/>
       <c r="AC230" s="272" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="AD230" s="124">
         <v>1.48</v>
@@ -19361,18 +19364,18 @@
         <v>12500</v>
       </c>
       <c r="AJ230" s="125" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AK230" s="352">
         <v>6000</v>
       </c>
       <c r="AQ230" s="323" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="231" spans="25:43" ht="15" customHeight="1">
       <c r="Y231" s="323" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="Z231" s="332" t="s">
         <v>135</v>
@@ -19380,7 +19383,7 @@
       <c r="AA231" s="107"/>
       <c r="AB231" s="107"/>
       <c r="AC231" s="271" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="AD231" s="125">
         <v>1.58</v>
@@ -19389,7 +19392,7 @@
         <v>12000</v>
       </c>
       <c r="AQ231" s="323" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="232" spans="25:43" ht="15" customHeight="1">
@@ -19399,7 +19402,7 @@
       <c r="AA232"/>
       <c r="AB232"/>
       <c r="AC232" s="271" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="AD232" s="125">
         <v>1.58</v>
@@ -19408,7 +19411,7 @@
         <v>11000</v>
       </c>
       <c r="AQ232" s="323" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="233" spans="25:43" ht="15" customHeight="1">
@@ -19418,7 +19421,7 @@
       <c r="AA233"/>
       <c r="AB233"/>
       <c r="AC233" s="271" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="AD233" s="125">
         <v>1.48</v>
@@ -19427,7 +19430,7 @@
         <v>11500</v>
       </c>
       <c r="AQ233" s="323" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="234" spans="25:43" ht="15" customHeight="1">
@@ -19437,7 +19440,7 @@
       <c r="AA234"/>
       <c r="AB234"/>
       <c r="AC234" s="272" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="AD234" s="124">
         <v>1.38</v>
@@ -19446,7 +19449,7 @@
         <v>10000</v>
       </c>
       <c r="AQ234" s="323" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="235" spans="25:43" ht="15" customHeight="1">
@@ -19456,7 +19459,7 @@
       <c r="AA235" s="107"/>
       <c r="AB235" s="107"/>
       <c r="AQ235" s="323" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="236" spans="25:43" ht="15" customHeight="1">
@@ -19466,7 +19469,7 @@
       <c r="AA236"/>
       <c r="AB236"/>
       <c r="AQ236" s="323" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="237" spans="25:43" ht="15" customHeight="1">
@@ -19476,7 +19479,7 @@
       <c r="AA237"/>
       <c r="AB237"/>
       <c r="AQ237" s="323" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="238" spans="25:43" ht="15" customHeight="1">
@@ -19486,7 +19489,7 @@
       <c r="AA238"/>
       <c r="AB238"/>
       <c r="AQ238" s="323" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="239" spans="25:43" ht="15" customHeight="1">
@@ -19496,7 +19499,7 @@
       <c r="AA239"/>
       <c r="AB239"/>
       <c r="AQ239" s="323" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="240" spans="25:43" ht="15" customHeight="1">
@@ -19506,7 +19509,7 @@
       <c r="AA240"/>
       <c r="AB240"/>
       <c r="AQ240" s="323" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="241" spans="26:43" ht="15" customHeight="1">
@@ -19516,7 +19519,7 @@
       <c r="AA241" s="59"/>
       <c r="AB241" s="59"/>
       <c r="AQ241" s="323" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="242" spans="26:43" ht="15" customHeight="1">
@@ -19526,7 +19529,7 @@
       <c r="AA242" s="107"/>
       <c r="AB242" s="107"/>
       <c r="AQ242" s="323" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="243" spans="26:43" ht="15" customHeight="1">
@@ -19536,7 +19539,7 @@
       <c r="AA243" s="68"/>
       <c r="AB243" s="68"/>
       <c r="AQ243" s="323" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="244" spans="26:43" ht="15" customHeight="1">
@@ -19546,7 +19549,7 @@
       <c r="AA244" s="68"/>
       <c r="AB244" s="68"/>
       <c r="AQ244" s="323" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="245" spans="26:43" ht="15" customHeight="1" thickBot="1">
@@ -19556,7 +19559,7 @@
       <c r="AA245" s="68"/>
       <c r="AB245" s="68"/>
       <c r="AQ245" s="323" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="246" spans="26:43" ht="15" customHeight="1">
@@ -19564,228 +19567,228 @@
         <v>119</v>
       </c>
       <c r="AQ246" s="323" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="247" spans="26:43" ht="15" customHeight="1">
       <c r="Z247" s="356"/>
       <c r="AQ247" s="323" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="248" spans="26:43" ht="15" customHeight="1">
       <c r="AQ248" s="323" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="249" spans="26:43" ht="15" customHeight="1">
       <c r="AQ249" s="323" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="250" spans="26:43" ht="15" customHeight="1">
       <c r="AQ250" s="323" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="251" spans="26:43" ht="15" customHeight="1">
       <c r="AQ251" s="323" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="252" spans="26:43" ht="15" customHeight="1">
       <c r="AQ252" s="323" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="253" spans="26:43" ht="15" customHeight="1">
       <c r="AQ253" s="323" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="254" spans="26:43" ht="15" customHeight="1">
       <c r="AQ254" s="323" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="255" spans="26:43" ht="15" customHeight="1">
       <c r="AQ255" s="323" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="256" spans="26:43" ht="15" customHeight="1">
       <c r="AQ256" s="323" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="257" spans="43:43" ht="15" customHeight="1">
       <c r="AQ257" s="323" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="258" spans="43:43" ht="15" customHeight="1">
       <c r="AQ258" s="323" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="259" spans="43:43" ht="15" customHeight="1">
       <c r="AQ259" s="323" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="260" spans="43:43" ht="15" customHeight="1">
       <c r="AQ260" s="323" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="261" spans="43:43" ht="15" customHeight="1">
       <c r="AQ261" s="323" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="262" spans="43:43" ht="15" customHeight="1">
       <c r="AQ262" s="323" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="263" spans="43:43" ht="15" customHeight="1">
       <c r="AQ263" s="323" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="264" spans="43:43" ht="15" customHeight="1">
       <c r="AQ264" s="323" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="265" spans="43:43" ht="15" customHeight="1">
       <c r="AQ265" s="323" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="266" spans="43:43" ht="15" customHeight="1">
       <c r="AQ266" s="323" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="267" spans="43:43" ht="15" customHeight="1">
       <c r="AQ267" s="323" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="268" spans="43:43" ht="15" customHeight="1">
       <c r="AQ268" s="323" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="269" spans="43:43" ht="15" customHeight="1">
       <c r="AQ269" s="323" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="270" spans="43:43" ht="15" customHeight="1">
       <c r="AQ270" s="323" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="271" spans="43:43" ht="15" customHeight="1">
       <c r="AQ271" s="323" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="272" spans="43:43" ht="15" customHeight="1">
       <c r="AQ272" s="323" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="273" spans="43:43" ht="15" customHeight="1">
       <c r="AQ273" s="323" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="274" spans="43:43" ht="15" customHeight="1">
       <c r="AQ274" s="323" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="275" spans="43:43" ht="15" customHeight="1">
       <c r="AQ275" s="323" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="276" spans="43:43" ht="15" customHeight="1">
       <c r="AQ276" s="323" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="277" spans="43:43" ht="15" customHeight="1">
       <c r="AQ277" s="323" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="278" spans="43:43" ht="15" customHeight="1">
       <c r="AQ278" s="323" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="279" spans="43:43" ht="15" customHeight="1">
       <c r="AQ279" s="323" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="280" spans="43:43" ht="15" customHeight="1">
       <c r="AQ280" s="323" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="281" spans="43:43" ht="15" customHeight="1">
       <c r="AQ281" s="323" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="282" spans="43:43" ht="15" customHeight="1">
       <c r="AQ282" s="323" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="283" spans="43:43" ht="15" customHeight="1">
       <c r="AQ283" s="323" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="284" spans="43:43" ht="15" customHeight="1">
       <c r="AQ284" s="323" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="285" spans="43:43" ht="15" customHeight="1">
       <c r="AQ285" s="323" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="286" spans="43:43" ht="15" customHeight="1">
       <c r="AQ286" s="323" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="287" spans="43:43" ht="15" customHeight="1">
       <c r="AQ287" s="323" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B4:J4"/>
+    <mergeCell ref="H1:I3"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="I5:L5"/>
     <mergeCell ref="C113:J113"/>
     <mergeCell ref="C114:J114"/>
     <mergeCell ref="C5:G5"/>
     <mergeCell ref="C6:G6"/>
     <mergeCell ref="C7:G7"/>
     <mergeCell ref="C112:J112"/>
-    <mergeCell ref="B4:J4"/>
-    <mergeCell ref="H1:I3"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="I5:L5"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AH4" xr:uid="{08873200-51AE-4F66-802C-DAE68045F71C}">
@@ -19850,20 +19853,20 @@
         <v>0</v>
       </c>
       <c r="J1" s="299"/>
-      <c r="AD1" s="477" t="s">
+      <c r="AD1" s="536" t="s">
         <v>1</v>
       </c>
-      <c r="AE1" s="478"/>
-      <c r="AF1" s="479"/>
-      <c r="AG1" s="477" t="s">
+      <c r="AE1" s="537"/>
+      <c r="AF1" s="538"/>
+      <c r="AG1" s="536" t="s">
         <v>93</v>
       </c>
-      <c r="AH1" s="478"/>
-      <c r="AI1" s="479"/>
-      <c r="AJ1" s="477" t="s">
+      <c r="AH1" s="537"/>
+      <c r="AI1" s="538"/>
+      <c r="AJ1" s="536" t="s">
         <v>56</v>
       </c>
-      <c r="AK1" s="479"/>
+      <c r="AK1" s="538"/>
     </row>
     <row r="2" spans="1:39" ht="30" customHeight="1">
       <c r="D2" s="60"/>
@@ -19924,11 +19927,11 @@
         <f>'Nota de venta'!C2</f>
         <v>0</v>
       </c>
-      <c r="D3" s="483"/>
-      <c r="E3" s="483"/>
-      <c r="F3" s="484"/>
-      <c r="G3" s="484"/>
-      <c r="H3" s="484"/>
+      <c r="D3" s="543"/>
+      <c r="E3" s="543"/>
+      <c r="F3" s="544"/>
+      <c r="G3" s="544"/>
+      <c r="H3" s="544"/>
       <c r="I3" s="103"/>
       <c r="J3" s="103"/>
       <c r="K3" s="62"/>
@@ -19977,16 +19980,16 @@
       </c>
     </row>
     <row r="4" spans="1:39" ht="27" customHeight="1">
-      <c r="B4" s="488" t="s">
+      <c r="B4" s="548" t="s">
         <v>45</v>
       </c>
-      <c r="C4" s="489"/>
-      <c r="D4" s="489"/>
-      <c r="E4" s="489"/>
-      <c r="F4" s="489"/>
-      <c r="G4" s="489"/>
-      <c r="H4" s="489"/>
-      <c r="I4" s="490"/>
+      <c r="C4" s="549"/>
+      <c r="D4" s="549"/>
+      <c r="E4" s="549"/>
+      <c r="F4" s="549"/>
+      <c r="G4" s="549"/>
+      <c r="H4" s="549"/>
+      <c r="I4" s="550"/>
       <c r="J4" s="308"/>
       <c r="K4" s="308"/>
       <c r="L4" s="308"/>
@@ -20034,21 +20037,21 @@
       <c r="B5" s="79" t="s">
         <v>101</v>
       </c>
-      <c r="C5" s="485">
+      <c r="C5" s="545">
         <f>'Nota de venta'!C5</f>
         <v>0</v>
       </c>
-      <c r="D5" s="485"/>
+      <c r="D5" s="545"/>
       <c r="E5" s="118"/>
-      <c r="F5" s="482" t="s">
-        <v>337</v>
-      </c>
-      <c r="G5" s="482"/>
-      <c r="H5" s="487">
+      <c r="F5" s="542" t="s">
+        <v>336</v>
+      </c>
+      <c r="G5" s="542"/>
+      <c r="H5" s="547">
         <f>'Nota de venta'!I6</f>
         <v>0</v>
       </c>
-      <c r="I5" s="487"/>
+      <c r="I5" s="547"/>
       <c r="J5" s="117"/>
       <c r="Y5" s="59" t="s">
         <v>64</v>
@@ -20091,21 +20094,21 @@
       <c r="B6" s="79" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="486">
+      <c r="C6" s="546">
         <f>'Nota de venta'!C6</f>
         <v>0</v>
       </c>
-      <c r="D6" s="486"/>
+      <c r="D6" s="546"/>
       <c r="E6" s="79"/>
-      <c r="F6" s="482" t="s">
-        <v>395</v>
-      </c>
-      <c r="G6" s="482"/>
-      <c r="H6" s="491">
+      <c r="F6" s="542" t="s">
+        <v>394</v>
+      </c>
+      <c r="G6" s="542"/>
+      <c r="H6" s="551">
         <f>'Nota de venta'!I5</f>
         <v>0</v>
       </c>
-      <c r="I6" s="491"/>
+      <c r="I6" s="551"/>
       <c r="AB6" s="134" t="s">
         <v>82</v>
       </c>
@@ -20143,20 +20146,20 @@
     </row>
     <row r="7" spans="1:39" ht="29" customHeight="1" thickBot="1">
       <c r="B7" s="79" t="s">
-        <v>621</v>
-      </c>
-      <c r="C7" s="480">
+        <v>620</v>
+      </c>
+      <c r="C7" s="540">
         <f>'Nota de venta'!C112</f>
         <v>0</v>
       </c>
-      <c r="D7" s="480"/>
+      <c r="D7" s="540"/>
       <c r="E7" s="64"/>
-      <c r="F7" s="482" t="s">
-        <v>396</v>
-      </c>
-      <c r="G7" s="482"/>
-      <c r="H7" s="481"/>
-      <c r="I7" s="481"/>
+      <c r="F7" s="542" t="s">
+        <v>395</v>
+      </c>
+      <c r="G7" s="542"/>
+      <c r="H7" s="541"/>
+      <c r="I7" s="541"/>
       <c r="J7" s="64"/>
       <c r="AB7" s="134" t="s">
         <v>65</v>
@@ -20194,18 +20197,18 @@
     </row>
     <row r="8" spans="1:39" ht="29" customHeight="1" thickBot="1">
       <c r="B8" s="79" t="s">
-        <v>619</v>
-      </c>
-      <c r="C8" s="503">
+        <v>618</v>
+      </c>
+      <c r="C8" s="539">
         <f>'Nota de venta'!C113</f>
         <v>0</v>
       </c>
-      <c r="D8" s="503"/>
-      <c r="E8" s="503"/>
-      <c r="F8" s="503"/>
-      <c r="G8" s="503"/>
-      <c r="H8" s="503"/>
-      <c r="I8" s="503"/>
+      <c r="D8" s="539"/>
+      <c r="E8" s="539"/>
+      <c r="F8" s="539"/>
+      <c r="G8" s="539"/>
+      <c r="H8" s="539"/>
+      <c r="I8" s="539"/>
       <c r="J8" s="64"/>
       <c r="AB8" s="134"/>
       <c r="AC8" s="136"/>
@@ -24157,11 +24160,11 @@
     </row>
     <row r="113" spans="1:27" ht="41" customHeight="1" thickBot="1">
       <c r="A113" s="62"/>
-      <c r="B113" s="492" t="s">
+      <c r="B113" s="526" t="s">
         <v>18</v>
       </c>
-      <c r="C113" s="493"/>
-      <c r="D113" s="494"/>
+      <c r="C113" s="527"/>
+      <c r="D113" s="528"/>
       <c r="E113" s="307"/>
       <c r="F113" s="72"/>
       <c r="G113" s="72"/>
@@ -24213,27 +24216,27 @@
     </row>
     <row r="117" spans="1:27" ht="50.25" customHeight="1">
       <c r="A117" s="62"/>
-      <c r="B117" s="495" t="s">
+      <c r="B117" s="529" t="s">
         <v>267</v>
       </c>
-      <c r="C117" s="496"/>
-      <c r="D117" s="496"/>
-      <c r="E117" s="496"/>
-      <c r="F117" s="496"/>
-      <c r="G117" s="496"/>
-      <c r="H117" s="496"/>
-      <c r="I117" s="496"/>
+      <c r="C117" s="530"/>
+      <c r="D117" s="530"/>
+      <c r="E117" s="530"/>
+      <c r="F117" s="530"/>
+      <c r="G117" s="530"/>
+      <c r="H117" s="530"/>
+      <c r="I117" s="530"/>
       <c r="AA117" s="73"/>
     </row>
     <row r="118" spans="1:27" ht="20" customHeight="1">
-      <c r="B118" s="496"/>
-      <c r="C118" s="496"/>
-      <c r="D118" s="496"/>
-      <c r="E118" s="496"/>
-      <c r="F118" s="496"/>
-      <c r="G118" s="496"/>
-      <c r="H118" s="496"/>
-      <c r="I118" s="496"/>
+      <c r="B118" s="530"/>
+      <c r="C118" s="530"/>
+      <c r="D118" s="530"/>
+      <c r="E118" s="530"/>
+      <c r="F118" s="530"/>
+      <c r="G118" s="530"/>
+      <c r="H118" s="530"/>
+      <c r="I118" s="530"/>
       <c r="J118" s="174"/>
       <c r="K118" s="174"/>
       <c r="L118" s="173"/>
@@ -24280,31 +24283,31 @@
       <c r="B122" s="172" t="s">
         <v>36</v>
       </c>
-      <c r="C122" s="501" t="s">
+      <c r="C122" s="535" t="s">
         <v>171</v>
       </c>
-      <c r="D122" s="502"/>
-      <c r="E122" s="502"/>
-      <c r="F122" s="502"/>
-      <c r="G122" s="502"/>
-      <c r="H122" s="502"/>
-      <c r="I122" s="496"/>
-      <c r="J122" s="496"/>
-      <c r="K122" s="496"/>
+      <c r="D122" s="503"/>
+      <c r="E122" s="503"/>
+      <c r="F122" s="503"/>
+      <c r="G122" s="503"/>
+      <c r="H122" s="503"/>
+      <c r="I122" s="530"/>
+      <c r="J122" s="530"/>
+      <c r="K122" s="530"/>
     </row>
     <row r="123" spans="1:27" ht="16.05" customHeight="1" thickBot="1"/>
     <row r="124" spans="1:27" ht="16.05" customHeight="1" thickBot="1">
       <c r="B124" s="59" t="s">
         <v>268</v>
       </c>
-      <c r="D124" s="497" t="s">
+      <c r="D124" s="531" t="s">
         <v>199</v>
       </c>
-      <c r="E124" s="498"/>
-      <c r="F124" s="499"/>
-      <c r="G124" s="499"/>
-      <c r="H124" s="499"/>
-      <c r="I124" s="500"/>
+      <c r="E124" s="532"/>
+      <c r="F124" s="533"/>
+      <c r="G124" s="533"/>
+      <c r="H124" s="533"/>
+      <c r="I124" s="534"/>
     </row>
     <row r="126" spans="1:27" ht="24" customHeight="1"/>
     <row r="129" ht="16.05" customHeight="1"/>
@@ -24357,12 +24360,6 @@
     <row r="220" ht="16.05" customHeight="1"/>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B113:D113"/>
-    <mergeCell ref="B117:I118"/>
-    <mergeCell ref="D124:I124"/>
-    <mergeCell ref="C122:K122"/>
-    <mergeCell ref="AD1:AF1"/>
-    <mergeCell ref="C8:I8"/>
     <mergeCell ref="AG1:AI1"/>
     <mergeCell ref="AJ1:AK1"/>
     <mergeCell ref="C7:D7"/>
@@ -24377,6 +24374,12 @@
     <mergeCell ref="B4:I4"/>
     <mergeCell ref="F7:G7"/>
     <mergeCell ref="H6:I6"/>
+    <mergeCell ref="B113:D113"/>
+    <mergeCell ref="B117:I118"/>
+    <mergeCell ref="D124:I124"/>
+    <mergeCell ref="C122:K122"/>
+    <mergeCell ref="AD1:AF1"/>
+    <mergeCell ref="C8:I8"/>
   </mergeCells>
   <pageMargins left="0.23734177215189872" right="0.70866141732283505" top="0.74803149606299202" bottom="0.74803149606299202" header="0.31496062992126" footer="0.31496062992126"/>
   <pageSetup scale="26" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292" r:id="rId1"/>
@@ -24417,14 +24420,14 @@
       <c r="F1" s="323"/>
       <c r="G1" s="323"/>
       <c r="H1" s="323"/>
-      <c r="I1" s="524" t="s">
+      <c r="I1" s="478" t="s">
         <v>120</v>
       </c>
-      <c r="J1" s="525">
+      <c r="J1" s="572">
         <f>'Nota de venta'!H1</f>
         <v>0</v>
       </c>
-      <c r="K1" s="526"/>
+      <c r="K1" s="573"/>
       <c r="L1" s="323"/>
       <c r="M1" s="323"/>
       <c r="N1" s="323"/>
@@ -24439,17 +24442,17 @@
       <c r="A2" s="323"/>
       <c r="B2" s="323"/>
       <c r="C2" s="323"/>
-      <c r="D2" s="529">
+      <c r="D2" s="576">
         <f>'Nota de venta'!C112</f>
         <v>0</v>
       </c>
-      <c r="E2" s="530"/>
-      <c r="F2" s="530"/>
-      <c r="G2" s="531"/>
+      <c r="E2" s="577"/>
+      <c r="F2" s="577"/>
+      <c r="G2" s="578"/>
       <c r="H2" s="323"/>
-      <c r="I2" s="524"/>
-      <c r="J2" s="527"/>
-      <c r="K2" s="528"/>
+      <c r="I2" s="478"/>
+      <c r="J2" s="574"/>
+      <c r="K2" s="575"/>
       <c r="L2" s="323"/>
       <c r="M2" s="323"/>
       <c r="N2" s="323"/>
@@ -24464,10 +24467,10 @@
       <c r="A3" s="323"/>
       <c r="B3" s="323"/>
       <c r="C3" s="323"/>
-      <c r="D3" s="532"/>
-      <c r="E3" s="533"/>
-      <c r="F3" s="533"/>
-      <c r="G3" s="534"/>
+      <c r="D3" s="579"/>
+      <c r="E3" s="580"/>
+      <c r="F3" s="580"/>
+      <c r="G3" s="581"/>
       <c r="H3" s="323"/>
       <c r="I3" s="144" t="s">
         <v>121</v>
@@ -24512,23 +24515,23 @@
       <c r="A5" s="121" t="s">
         <v>123</v>
       </c>
-      <c r="B5" s="522">
+      <c r="B5" s="570">
         <f>'Nota de venta'!C6</f>
         <v>0</v>
       </c>
-      <c r="C5" s="523"/>
-      <c r="D5" s="523"/>
+      <c r="C5" s="571"/>
+      <c r="D5" s="571"/>
       <c r="E5" s="427"/>
       <c r="F5" s="426"/>
       <c r="H5" s="323"/>
       <c r="I5" s="144" t="s">
-        <v>402</v>
-      </c>
-      <c r="J5" s="535">
+        <v>401</v>
+      </c>
+      <c r="J5" s="504">
         <f>'Nota de venta'!C5</f>
         <v>0</v>
       </c>
-      <c r="K5" s="536"/>
+      <c r="K5" s="505"/>
       <c r="L5" s="323"/>
       <c r="M5" s="323"/>
       <c r="N5" s="323"/>
@@ -24563,21 +24566,21 @@
     </row>
     <row r="7" spans="1:40" ht="18" customHeight="1" thickBot="1">
       <c r="A7" s="121" t="s">
-        <v>618</v>
-      </c>
-      <c r="B7" s="519">
+        <v>617</v>
+      </c>
+      <c r="B7" s="567">
         <f>'Nota de venta'!C114</f>
         <v>0</v>
       </c>
-      <c r="C7" s="520"/>
-      <c r="D7" s="520"/>
-      <c r="E7" s="520"/>
-      <c r="F7" s="520"/>
-      <c r="G7" s="520"/>
-      <c r="H7" s="520"/>
-      <c r="I7" s="520"/>
-      <c r="J7" s="520"/>
-      <c r="K7" s="521"/>
+      <c r="C7" s="568"/>
+      <c r="D7" s="568"/>
+      <c r="E7" s="568"/>
+      <c r="F7" s="568"/>
+      <c r="G7" s="568"/>
+      <c r="H7" s="568"/>
+      <c r="I7" s="568"/>
+      <c r="J7" s="568"/>
+      <c r="K7" s="569"/>
       <c r="L7" s="323"/>
       <c r="M7" s="323"/>
       <c r="N7" s="323"/>
@@ -24589,10 +24592,10 @@
       <c r="T7" s="323"/>
     </row>
     <row r="8" spans="1:40" s="119" customFormat="1" ht="16.149999999999999" thickBot="1">
-      <c r="C8" s="543"/>
-      <c r="D8" s="543"/>
-      <c r="E8" s="543"/>
-      <c r="F8" s="543"/>
+      <c r="C8" s="557"/>
+      <c r="D8" s="557"/>
+      <c r="E8" s="557"/>
+      <c r="F8" s="557"/>
       <c r="J8" s="372"/>
       <c r="K8" s="372"/>
       <c r="L8" s="372"/>
@@ -24623,19 +24626,19 @@
       <c r="AK8" s="120"/>
       <c r="AL8" s="120"/>
       <c r="AM8" s="373" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AN8" s="120"/>
     </row>
     <row r="9" spans="1:40" s="119" customFormat="1" ht="15.4" thickBot="1">
       <c r="A9" s="455" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B9" s="440" t="s">
         <v>72</v>
       </c>
       <c r="C9" s="441" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D9" s="441" t="s">
         <v>298</v>
@@ -24647,15 +24650,15 @@
         <v>7</v>
       </c>
       <c r="G9" s="439" t="s">
+        <v>404</v>
+      </c>
+      <c r="H9" s="558" t="s">
         <v>405</v>
       </c>
-      <c r="H9" s="544" t="s">
-        <v>406</v>
-      </c>
-      <c r="I9" s="544"/>
-      <c r="J9" s="544"/>
-      <c r="K9" s="544"/>
-      <c r="L9" s="544"/>
+      <c r="I9" s="558"/>
+      <c r="J9" s="558"/>
+      <c r="K9" s="558"/>
+      <c r="L9" s="558"/>
       <c r="M9" s="408"/>
       <c r="N9" s="408"/>
       <c r="O9" s="408"/>
@@ -24713,11 +24716,11 @@
         <f>NotaDeVenta[[#This Row],[ML impresos]]</f>
         <v>0</v>
       </c>
-      <c r="H10" s="545"/>
-      <c r="I10" s="546"/>
-      <c r="J10" s="546"/>
-      <c r="K10" s="546"/>
-      <c r="L10" s="546"/>
+      <c r="H10" s="559"/>
+      <c r="I10" s="560"/>
+      <c r="J10" s="560"/>
+      <c r="K10" s="560"/>
+      <c r="L10" s="560"/>
       <c r="M10" s="408"/>
       <c r="N10" s="408"/>
       <c r="O10" s="408"/>
@@ -30974,7 +30977,7 @@
       <c r="S111" s="323"/>
       <c r="T111" s="323"/>
       <c r="AM111" s="120" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="112" spans="1:39" ht="14.65" thickBot="1">
@@ -30999,7 +31002,7 @@
     </row>
     <row r="113" spans="1:40" ht="21.4" thickBot="1">
       <c r="A113" s="375" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B113" s="401"/>
       <c r="C113" s="431"/>
@@ -31008,7 +31011,7 @@
       <c r="F113" s="323"/>
       <c r="G113" s="323"/>
       <c r="H113" s="415" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="I113" s="428"/>
       <c r="J113" s="428"/>
@@ -31025,13 +31028,13 @@
     </row>
     <row r="114" spans="1:40" ht="15.75" thickBot="1">
       <c r="A114" s="375" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B114" s="401"/>
       <c r="C114" s="376"/>
       <c r="D114" s="160"/>
       <c r="E114" s="160" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="F114" s="377"/>
       <c r="G114" s="378"/>
@@ -31051,14 +31054,14 @@
     </row>
     <row r="115" spans="1:40" ht="20.65" thickBot="1">
       <c r="A115" s="379" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B115" s="160"/>
-      <c r="C115" s="547"/>
-      <c r="D115" s="547"/>
-      <c r="E115" s="547"/>
-      <c r="F115" s="548"/>
-      <c r="G115" s="549"/>
+      <c r="C115" s="561"/>
+      <c r="D115" s="561"/>
+      <c r="E115" s="561"/>
+      <c r="F115" s="562"/>
+      <c r="G115" s="563"/>
       <c r="H115" s="323"/>
       <c r="I115" s="323"/>
       <c r="J115" s="429"/>
@@ -31075,14 +31078,14 @@
     </row>
     <row r="116" spans="1:40" ht="20.65" thickBot="1">
       <c r="A116" s="379" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B116" s="402"/>
-      <c r="C116" s="550"/>
-      <c r="D116" s="551"/>
-      <c r="E116" s="551"/>
-      <c r="F116" s="551"/>
-      <c r="G116" s="552"/>
+      <c r="C116" s="564"/>
+      <c r="D116" s="565"/>
+      <c r="E116" s="565"/>
+      <c r="F116" s="565"/>
+      <c r="G116" s="566"/>
       <c r="H116" s="323"/>
       <c r="I116" s="323"/>
       <c r="J116" s="429"/>
@@ -31098,17 +31101,17 @@
       <c r="T116" s="323"/>
     </row>
     <row r="117" spans="1:40" s="119" customFormat="1" ht="20.65">
-      <c r="A117" s="537"/>
-      <c r="B117" s="537"/>
-      <c r="C117" s="538"/>
-      <c r="D117" s="538"/>
-      <c r="E117" s="539"/>
-      <c r="F117" s="540"/>
-      <c r="G117" s="541"/>
-      <c r="H117" s="542"/>
-      <c r="I117" s="542"/>
-      <c r="J117" s="542"/>
-      <c r="K117" s="542"/>
+      <c r="A117" s="502"/>
+      <c r="B117" s="502"/>
+      <c r="C117" s="552"/>
+      <c r="D117" s="552"/>
+      <c r="E117" s="553"/>
+      <c r="F117" s="554"/>
+      <c r="G117" s="555"/>
+      <c r="H117" s="556"/>
+      <c r="I117" s="556"/>
+      <c r="J117" s="556"/>
+      <c r="K117" s="556"/>
       <c r="L117"/>
       <c r="M117" s="408"/>
       <c r="N117" s="408"/>
@@ -31154,6 +31157,12 @@
     <row r="126" spans="1:40" ht="33" hidden="1" customHeight="1"/>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="B7:K7"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:K2"/>
+    <mergeCell ref="D2:G3"/>
+    <mergeCell ref="J5:K5"/>
     <mergeCell ref="A117:D117"/>
     <mergeCell ref="E117:F117"/>
     <mergeCell ref="G117:K117"/>
@@ -31163,12 +31172,6 @@
     <mergeCell ref="C115:E115"/>
     <mergeCell ref="F115:G115"/>
     <mergeCell ref="C116:G116"/>
-    <mergeCell ref="B7:K7"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:K2"/>
-    <mergeCell ref="D2:G3"/>
-    <mergeCell ref="J5:K5"/>
   </mergeCells>
   <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C111" xr:uid="{505AF3CD-CB27-48B9-9280-8169DA8BC7DA}">
@@ -31217,14 +31220,14 @@
       <c r="F1" s="323"/>
       <c r="G1" s="323"/>
       <c r="H1" s="323"/>
-      <c r="I1" s="524" t="s">
+      <c r="I1" s="478" t="s">
         <v>120</v>
       </c>
-      <c r="J1" s="579">
+      <c r="J1" s="507">
         <f>'Nota de venta'!H1</f>
         <v>0</v>
       </c>
-      <c r="K1" s="580"/>
+      <c r="K1" s="508"/>
       <c r="L1" s="432"/>
       <c r="M1" s="323"/>
       <c r="O1" s="323"/>
@@ -31253,17 +31256,17 @@
     <row r="2" spans="1:32" ht="16.05" customHeight="1" thickBot="1">
       <c r="A2" s="323"/>
       <c r="C2" s="323"/>
-      <c r="D2" s="572">
+      <c r="D2" s="496">
         <f>'Nota de venta'!C112</f>
         <v>0</v>
       </c>
-      <c r="E2" s="573"/>
-      <c r="F2" s="573"/>
-      <c r="G2" s="574"/>
+      <c r="E2" s="497"/>
+      <c r="F2" s="497"/>
+      <c r="G2" s="498"/>
       <c r="H2" s="323"/>
-      <c r="I2" s="524"/>
-      <c r="J2" s="581"/>
-      <c r="K2" s="582"/>
+      <c r="I2" s="478"/>
+      <c r="J2" s="509"/>
+      <c r="K2" s="510"/>
       <c r="L2" s="432"/>
       <c r="M2" s="323"/>
       <c r="N2" s="323"/>
@@ -31293,15 +31296,15 @@
     <row r="3" spans="1:32" ht="33" customHeight="1" thickBot="1">
       <c r="A3" s="323"/>
       <c r="C3" s="323"/>
-      <c r="D3" s="575"/>
-      <c r="E3" s="576"/>
-      <c r="F3" s="576"/>
-      <c r="G3" s="577"/>
+      <c r="D3" s="499"/>
+      <c r="E3" s="500"/>
+      <c r="F3" s="500"/>
+      <c r="G3" s="501"/>
       <c r="I3" s="144" t="s">
         <v>121</v>
       </c>
-      <c r="J3" s="570"/>
-      <c r="K3" s="571"/>
+      <c r="J3" s="494"/>
+      <c r="K3" s="495"/>
       <c r="L3" s="420"/>
       <c r="M3" s="323"/>
       <c r="N3" s="323"/>
@@ -31333,13 +31336,13 @@
       <c r="D4" s="323"/>
       <c r="E4" s="323"/>
       <c r="F4" s="323"/>
-      <c r="G4" s="559"/>
-      <c r="H4" s="560"/>
+      <c r="G4" s="483"/>
+      <c r="H4" s="484"/>
       <c r="I4" s="144" t="s">
         <v>122</v>
       </c>
-      <c r="J4" s="570"/>
-      <c r="K4" s="571"/>
+      <c r="J4" s="494"/>
+      <c r="K4" s="495"/>
       <c r="L4" s="395"/>
       <c r="M4" s="323"/>
       <c r="N4" s="323"/>
@@ -31369,13 +31372,13 @@
       <c r="B5" s="121" t="s">
         <v>123</v>
       </c>
-      <c r="C5" s="535">
+      <c r="C5" s="504">
         <f>'Nota de venta'!C6</f>
         <v>0</v>
       </c>
-      <c r="D5" s="536"/>
-      <c r="E5" s="536"/>
-      <c r="F5" s="578"/>
+      <c r="D5" s="505"/>
+      <c r="E5" s="505"/>
+      <c r="F5" s="506"/>
       <c r="G5" s="323"/>
       <c r="H5" s="323"/>
       <c r="J5" s="323"/>
@@ -31406,23 +31409,23 @@
     </row>
     <row r="6" spans="1:32" ht="33.75" customHeight="1" thickBot="1">
       <c r="A6" s="323"/>
-      <c r="B6" s="555" t="s">
+      <c r="B6" s="479" t="s">
         <v>328</v>
       </c>
-      <c r="C6" s="555">
+      <c r="C6" s="479">
         <f>'Nota de venta'!C114</f>
         <v>0</v>
       </c>
-      <c r="D6" s="564"/>
-      <c r="E6" s="564"/>
-      <c r="F6" s="565"/>
+      <c r="D6" s="488"/>
+      <c r="E6" s="488"/>
+      <c r="F6" s="489"/>
       <c r="G6" s="323"/>
       <c r="H6" s="323"/>
       <c r="I6" s="393" t="s">
         <v>208</v>
       </c>
-      <c r="J6" s="568"/>
-      <c r="K6" s="569"/>
+      <c r="J6" s="492"/>
+      <c r="K6" s="493"/>
       <c r="L6" s="419"/>
       <c r="M6" s="323"/>
       <c r="N6" s="323"/>
@@ -31449,19 +31452,19 @@
     </row>
     <row r="7" spans="1:32" ht="33.4" customHeight="1" thickBot="1">
       <c r="A7" s="323"/>
-      <c r="B7" s="556"/>
-      <c r="C7" s="556"/>
-      <c r="D7" s="566"/>
-      <c r="E7" s="566"/>
-      <c r="F7" s="567"/>
+      <c r="B7" s="480"/>
+      <c r="C7" s="480"/>
+      <c r="D7" s="490"/>
+      <c r="E7" s="490"/>
+      <c r="F7" s="491"/>
       <c r="G7" s="418"/>
       <c r="H7" s="418"/>
       <c r="I7" s="309"/>
-      <c r="J7" s="537" t="s">
+      <c r="J7" s="502" t="s">
         <v>329</v>
       </c>
-      <c r="K7" s="502"/>
-      <c r="L7" s="502"/>
+      <c r="K7" s="503"/>
+      <c r="L7" s="503"/>
       <c r="M7" s="323"/>
       <c r="N7" s="323"/>
       <c r="O7" s="323"/>
@@ -31522,7 +31525,7 @@
         <v>175</v>
       </c>
       <c r="N8" s="255" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="O8" s="59"/>
       <c r="P8" s="408"/>
@@ -38991,22 +38994,22 @@
       <c r="B112" s="158" t="s">
         <v>269</v>
       </c>
-      <c r="C112" s="561"/>
-      <c r="D112" s="562"/>
-      <c r="E112" s="563"/>
+      <c r="C112" s="485"/>
+      <c r="D112" s="486"/>
+      <c r="E112" s="487"/>
       <c r="F112" s="413"/>
       <c r="G112" s="413"/>
       <c r="H112" s="414"/>
       <c r="I112" s="415"/>
       <c r="J112" s="415"/>
       <c r="K112" s="416"/>
-      <c r="L112" s="553"/>
-      <c r="M112" s="554"/>
+      <c r="L112" s="476"/>
+      <c r="M112" s="477"/>
     </row>
     <row r="113" spans="2:20" s="323" customFormat="1" ht="19.05" customHeight="1"/>
     <row r="114" spans="2:20" ht="24" customHeight="1">
       <c r="B114" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C114" t="e">
         <f>J109/'Nota de venta'!D10</f>
@@ -39062,8 +39065,8 @@
       <c r="D127" s="160"/>
       <c r="E127" s="155"/>
       <c r="F127" s="162"/>
-      <c r="G127" s="557"/>
-      <c r="H127" s="558"/>
+      <c r="G127" s="481"/>
+      <c r="H127" s="482"/>
       <c r="I127" s="160"/>
       <c r="K127" s="161"/>
     </row>
@@ -39163,30 +39166,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:36" ht="40.5" customHeight="1">
-      <c r="C1" s="607" t="s">
+      <c r="C1" s="588" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="607"/>
-      <c r="E1" s="607"/>
-      <c r="F1" s="607"/>
+      <c r="D1" s="588"/>
+      <c r="E1" s="588"/>
+      <c r="F1" s="588"/>
       <c r="G1" s="11" t="s">
         <v>0</v>
       </c>
       <c r="H1" s="43"/>
-      <c r="Z1" s="603" t="s">
+      <c r="Z1" s="582" t="s">
         <v>1</v>
       </c>
-      <c r="AA1" s="604"/>
-      <c r="AB1" s="605"/>
-      <c r="AC1" s="603" t="s">
+      <c r="AA1" s="583"/>
+      <c r="AB1" s="584"/>
+      <c r="AC1" s="582" t="s">
         <v>93</v>
       </c>
-      <c r="AD1" s="604"/>
-      <c r="AE1" s="605"/>
-      <c r="AF1" s="603" t="s">
+      <c r="AD1" s="583"/>
+      <c r="AE1" s="584"/>
+      <c r="AF1" s="582" t="s">
         <v>56</v>
       </c>
-      <c r="AG1" s="605"/>
+      <c r="AG1" s="584"/>
     </row>
     <row r="2" spans="1:36" ht="30" customHeight="1">
       <c r="C2" s="35"/>
@@ -39247,12 +39250,12 @@
         <v>81</v>
       </c>
       <c r="B3" s="38"/>
-      <c r="C3" s="601" t="s">
+      <c r="C3" s="589" t="s">
         <v>59</v>
       </c>
-      <c r="D3" s="602"/>
-      <c r="E3" s="610"/>
-      <c r="F3" s="610"/>
+      <c r="D3" s="590"/>
+      <c r="E3" s="593"/>
+      <c r="F3" s="593"/>
       <c r="G3" s="10" t="s">
         <v>80</v>
       </c>
@@ -39354,16 +39357,16 @@
       <c r="AJ4" s="12"/>
     </row>
     <row r="5" spans="1:36">
-      <c r="A5" s="587" t="s">
+      <c r="A5" s="594" t="s">
         <v>45</v>
       </c>
-      <c r="B5" s="587"/>
-      <c r="C5" s="587"/>
-      <c r="D5" s="587"/>
-      <c r="E5" s="587"/>
-      <c r="F5" s="587"/>
-      <c r="G5" s="587"/>
-      <c r="H5" s="587"/>
+      <c r="B5" s="594"/>
+      <c r="C5" s="594"/>
+      <c r="D5" s="594"/>
+      <c r="E5" s="594"/>
+      <c r="F5" s="594"/>
+      <c r="G5" s="594"/>
+      <c r="H5" s="594"/>
       <c r="U5" s="12" t="s">
         <v>64</v>
       </c>
@@ -39408,12 +39411,12 @@
         <v>46</v>
       </c>
       <c r="B6" s="40"/>
-      <c r="C6" s="601" t="s">
+      <c r="C6" s="589" t="s">
         <v>67</v>
       </c>
-      <c r="D6" s="602"/>
-      <c r="E6" s="609"/>
-      <c r="F6" s="609"/>
+      <c r="D6" s="590"/>
+      <c r="E6" s="592"/>
+      <c r="F6" s="592"/>
       <c r="G6" s="10" t="s">
         <v>68</v>
       </c>
@@ -39462,12 +39465,12 @@
         <v>90</v>
       </c>
       <c r="B7" s="41"/>
-      <c r="C7" s="601" t="s">
+      <c r="C7" s="589" t="s">
         <v>55</v>
       </c>
-      <c r="D7" s="602"/>
-      <c r="E7" s="608"/>
-      <c r="F7" s="608"/>
+      <c r="D7" s="590"/>
+      <c r="E7" s="591"/>
+      <c r="F7" s="591"/>
       <c r="G7" s="10" t="s">
         <v>29</v>
       </c>
@@ -39513,12 +39516,12 @@
         <v>48</v>
       </c>
       <c r="B8" s="41"/>
-      <c r="C8" s="601" t="s">
+      <c r="C8" s="589" t="s">
         <v>49</v>
       </c>
-      <c r="D8" s="602"/>
-      <c r="E8" s="608"/>
-      <c r="F8" s="608"/>
+      <c r="D8" s="590"/>
+      <c r="E8" s="591"/>
+      <c r="F8" s="591"/>
       <c r="G8" s="10" t="s">
         <v>108</v>
       </c>
@@ -39559,12 +39562,12 @@
         <v>76</v>
       </c>
       <c r="B9" s="41"/>
-      <c r="C9" s="601" t="s">
+      <c r="C9" s="589" t="s">
         <v>77</v>
       </c>
-      <c r="D9" s="602"/>
-      <c r="E9" s="608"/>
-      <c r="F9" s="608"/>
+      <c r="D9" s="590"/>
+      <c r="E9" s="591"/>
+      <c r="F9" s="591"/>
       <c r="G9" s="10" t="s">
         <v>5</v>
       </c>
@@ -39617,16 +39620,16 @@
       <c r="AG10" s="10"/>
     </row>
     <row r="11" spans="1:36">
-      <c r="A11" s="587" t="s">
+      <c r="A11" s="594" t="s">
         <v>98</v>
       </c>
-      <c r="B11" s="587"/>
-      <c r="C11" s="587"/>
-      <c r="D11" s="587"/>
-      <c r="E11" s="587"/>
-      <c r="F11" s="587"/>
-      <c r="G11" s="587"/>
-      <c r="H11" s="587"/>
+      <c r="B11" s="594"/>
+      <c r="C11" s="594"/>
+      <c r="D11" s="594"/>
+      <c r="E11" s="594"/>
+      <c r="F11" s="594"/>
+      <c r="G11" s="594"/>
+      <c r="H11" s="594"/>
       <c r="X11" s="10"/>
       <c r="Y11" s="10"/>
       <c r="Z11" s="10"/>
@@ -39643,12 +39646,12 @@
       <c r="B12" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="585"/>
-      <c r="D12" s="585"/>
-      <c r="E12" s="585"/>
-      <c r="F12" s="585"/>
-      <c r="G12" s="585"/>
-      <c r="H12" s="585"/>
+      <c r="C12" s="596"/>
+      <c r="D12" s="596"/>
+      <c r="E12" s="596"/>
+      <c r="F12" s="596"/>
+      <c r="G12" s="596"/>
+      <c r="H12" s="596"/>
     </row>
     <row r="13" spans="1:36">
       <c r="B13" s="25"/>
@@ -39660,42 +39663,42 @@
       <c r="H13" s="25"/>
     </row>
     <row r="14" spans="1:36">
-      <c r="A14" s="587" t="s">
+      <c r="A14" s="594" t="s">
         <v>69</v>
       </c>
-      <c r="B14" s="587"/>
-      <c r="C14" s="587"/>
-      <c r="D14" s="587"/>
-      <c r="E14" s="587"/>
-      <c r="F14" s="587"/>
-      <c r="G14" s="587"/>
-      <c r="H14" s="587"/>
+      <c r="B14" s="594"/>
+      <c r="C14" s="594"/>
+      <c r="D14" s="594"/>
+      <c r="E14" s="594"/>
+      <c r="F14" s="594"/>
+      <c r="G14" s="594"/>
+      <c r="H14" s="594"/>
     </row>
     <row r="15" spans="1:36" ht="18.75" customHeight="1">
       <c r="A15" s="10" t="s">
         <v>62</v>
       </c>
       <c r="B15" s="37"/>
-      <c r="C15" s="601" t="s">
+      <c r="C15" s="589" t="s">
         <v>17</v>
       </c>
-      <c r="D15" s="602"/>
-      <c r="E15" s="583"/>
-      <c r="F15" s="584"/>
-      <c r="G15" s="584"/>
-      <c r="H15" s="606"/>
+      <c r="D15" s="590"/>
+      <c r="E15" s="585"/>
+      <c r="F15" s="586"/>
+      <c r="G15" s="586"/>
+      <c r="H15" s="587"/>
     </row>
     <row r="16" spans="1:36" ht="18.75" customHeight="1">
       <c r="A16" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="583"/>
-      <c r="C16" s="584"/>
-      <c r="D16" s="584"/>
-      <c r="E16" s="584"/>
-      <c r="F16" s="584"/>
-      <c r="G16" s="584"/>
-      <c r="H16" s="606"/>
+      <c r="B16" s="585"/>
+      <c r="C16" s="586"/>
+      <c r="D16" s="586"/>
+      <c r="E16" s="586"/>
+      <c r="F16" s="586"/>
+      <c r="G16" s="586"/>
+      <c r="H16" s="587"/>
       <c r="X16" s="26"/>
     </row>
     <row r="17" spans="1:24" ht="15" customHeight="1">
@@ -39709,16 +39712,16 @@
       <c r="X17" s="26"/>
     </row>
     <row r="18" spans="1:24">
-      <c r="A18" s="587" t="s">
+      <c r="A18" s="594" t="s">
         <v>51</v>
       </c>
-      <c r="B18" s="587"/>
-      <c r="C18" s="587"/>
-      <c r="D18" s="587"/>
-      <c r="E18" s="587"/>
-      <c r="F18" s="587"/>
-      <c r="G18" s="587"/>
-      <c r="H18" s="587"/>
+      <c r="B18" s="594"/>
+      <c r="C18" s="594"/>
+      <c r="D18" s="594"/>
+      <c r="E18" s="594"/>
+      <c r="F18" s="594"/>
+      <c r="G18" s="594"/>
+      <c r="H18" s="594"/>
     </row>
     <row r="19" spans="1:24" ht="18.75" customHeight="1">
       <c r="A19" s="10" t="s">
@@ -39739,16 +39742,16 @@
       <c r="H19" s="33"/>
     </row>
     <row r="21" spans="1:24">
-      <c r="A21" s="587" t="s">
+      <c r="A21" s="594" t="s">
         <v>11</v>
       </c>
-      <c r="B21" s="587"/>
-      <c r="C21" s="587"/>
-      <c r="D21" s="587"/>
-      <c r="E21" s="587"/>
-      <c r="F21" s="587"/>
-      <c r="G21" s="587"/>
-      <c r="H21" s="587"/>
+      <c r="B21" s="594"/>
+      <c r="C21" s="594"/>
+      <c r="D21" s="594"/>
+      <c r="E21" s="594"/>
+      <c r="F21" s="594"/>
+      <c r="G21" s="594"/>
+      <c r="H21" s="594"/>
     </row>
     <row r="22" spans="1:24">
       <c r="A22" s="25" t="s">
@@ -39927,30 +39930,30 @@
       <c r="H30" s="31"/>
     </row>
     <row r="31" spans="1:24">
-      <c r="A31" s="587" t="s">
+      <c r="A31" s="594" t="s">
         <v>85</v>
       </c>
-      <c r="B31" s="587"/>
-      <c r="C31" s="587"/>
-      <c r="D31" s="587"/>
-      <c r="E31" s="587"/>
-      <c r="F31" s="587"/>
-      <c r="G31" s="587"/>
-      <c r="H31" s="587"/>
+      <c r="B31" s="594"/>
+      <c r="C31" s="594"/>
+      <c r="D31" s="594"/>
+      <c r="E31" s="594"/>
+      <c r="F31" s="594"/>
+      <c r="G31" s="594"/>
+      <c r="H31" s="594"/>
     </row>
     <row r="32" spans="1:24" ht="18.75" customHeight="1">
       <c r="A32" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="B32" s="600"/>
-      <c r="C32" s="600"/>
-      <c r="D32" s="600"/>
-      <c r="E32" s="601" t="s">
+      <c r="B32" s="595"/>
+      <c r="C32" s="595"/>
+      <c r="D32" s="595"/>
+      <c r="E32" s="589" t="s">
         <v>112</v>
       </c>
-      <c r="F32" s="602"/>
-      <c r="G32" s="600"/>
-      <c r="H32" s="600"/>
+      <c r="F32" s="590"/>
+      <c r="G32" s="595"/>
+      <c r="H32" s="595"/>
     </row>
     <row r="33" spans="1:24">
       <c r="B33" s="21"/>
@@ -39962,26 +39965,26 @@
       <c r="H33" s="21"/>
     </row>
     <row r="34" spans="1:24">
-      <c r="A34" s="587" t="s">
+      <c r="A34" s="594" t="s">
         <v>94</v>
       </c>
-      <c r="B34" s="587"/>
-      <c r="C34" s="587"/>
-      <c r="D34" s="587"/>
-      <c r="E34" s="587"/>
-      <c r="F34" s="587"/>
-      <c r="G34" s="587"/>
-      <c r="H34" s="587"/>
+      <c r="B34" s="594"/>
+      <c r="C34" s="594"/>
+      <c r="D34" s="594"/>
+      <c r="E34" s="594"/>
+      <c r="F34" s="594"/>
+      <c r="G34" s="594"/>
+      <c r="H34" s="594"/>
     </row>
     <row r="35" spans="1:24" ht="18.75" customHeight="1">
       <c r="A35" s="10" t="s">
         <v>47</v>
       </c>
       <c r="B35" s="52"/>
-      <c r="C35" s="583" t="s">
+      <c r="C35" s="585" t="s">
         <v>26</v>
       </c>
-      <c r="D35" s="584"/>
+      <c r="D35" s="586"/>
       <c r="E35" s="34"/>
       <c r="F35" s="34"/>
       <c r="G35" s="34"/>
@@ -39993,12 +39996,12 @@
         <v>97</v>
       </c>
       <c r="B36" s="36"/>
-      <c r="C36" s="588"/>
-      <c r="D36" s="589"/>
-      <c r="E36" s="589"/>
-      <c r="F36" s="589"/>
-      <c r="G36" s="589"/>
-      <c r="H36" s="590"/>
+      <c r="C36" s="598"/>
+      <c r="D36" s="599"/>
+      <c r="E36" s="599"/>
+      <c r="F36" s="599"/>
+      <c r="G36" s="599"/>
+      <c r="H36" s="600"/>
       <c r="X36" s="32"/>
     </row>
     <row r="37" spans="1:24" ht="18.75" customHeight="1">
@@ -40006,12 +40009,12 @@
         <v>4</v>
       </c>
       <c r="B37" s="36"/>
-      <c r="C37" s="591"/>
-      <c r="D37" s="592"/>
-      <c r="E37" s="592"/>
-      <c r="F37" s="592"/>
-      <c r="G37" s="592"/>
-      <c r="H37" s="593"/>
+      <c r="C37" s="601"/>
+      <c r="D37" s="602"/>
+      <c r="E37" s="602"/>
+      <c r="F37" s="602"/>
+      <c r="G37" s="602"/>
+      <c r="H37" s="603"/>
       <c r="X37" s="32"/>
     </row>
     <row r="38" spans="1:24" ht="18.75" customHeight="1">
@@ -40019,12 +40022,12 @@
         <v>14</v>
       </c>
       <c r="B38" s="36"/>
-      <c r="C38" s="591"/>
-      <c r="D38" s="592"/>
-      <c r="E38" s="592"/>
-      <c r="F38" s="592"/>
-      <c r="G38" s="592"/>
-      <c r="H38" s="593"/>
+      <c r="C38" s="601"/>
+      <c r="D38" s="602"/>
+      <c r="E38" s="602"/>
+      <c r="F38" s="602"/>
+      <c r="G38" s="602"/>
+      <c r="H38" s="603"/>
       <c r="X38" s="32"/>
     </row>
     <row r="39" spans="1:24" ht="18.75" customHeight="1">
@@ -40032,12 +40035,12 @@
         <v>83</v>
       </c>
       <c r="B39" s="36"/>
-      <c r="C39" s="591"/>
-      <c r="D39" s="592"/>
-      <c r="E39" s="592"/>
-      <c r="F39" s="592"/>
-      <c r="G39" s="592"/>
-      <c r="H39" s="593"/>
+      <c r="C39" s="601"/>
+      <c r="D39" s="602"/>
+      <c r="E39" s="602"/>
+      <c r="F39" s="602"/>
+      <c r="G39" s="602"/>
+      <c r="H39" s="603"/>
       <c r="X39" s="32"/>
     </row>
     <row r="40" spans="1:24" ht="18.75" customHeight="1">
@@ -40045,12 +40048,12 @@
         <v>33</v>
       </c>
       <c r="B40" s="36"/>
-      <c r="C40" s="591"/>
-      <c r="D40" s="592"/>
-      <c r="E40" s="592"/>
-      <c r="F40" s="592"/>
-      <c r="G40" s="592"/>
-      <c r="H40" s="593"/>
+      <c r="C40" s="601"/>
+      <c r="D40" s="602"/>
+      <c r="E40" s="602"/>
+      <c r="F40" s="602"/>
+      <c r="G40" s="602"/>
+      <c r="H40" s="603"/>
       <c r="X40" s="32"/>
     </row>
     <row r="41" spans="1:24" ht="18.75" customHeight="1">
@@ -40058,12 +40061,12 @@
         <v>34</v>
       </c>
       <c r="B41" s="36"/>
-      <c r="C41" s="594"/>
-      <c r="D41" s="595"/>
-      <c r="E41" s="595"/>
-      <c r="F41" s="595"/>
-      <c r="G41" s="595"/>
-      <c r="H41" s="596"/>
+      <c r="C41" s="604"/>
+      <c r="D41" s="605"/>
+      <c r="E41" s="605"/>
+      <c r="F41" s="605"/>
+      <c r="G41" s="605"/>
+      <c r="H41" s="606"/>
       <c r="X41" s="32"/>
     </row>
     <row r="42" spans="1:24" ht="18.75" customHeight="1">
@@ -40071,14 +40074,14 @@
         <v>21</v>
       </c>
       <c r="B42" s="36"/>
-      <c r="C42" s="592" t="s">
+      <c r="C42" s="602" t="s">
         <v>9</v>
       </c>
-      <c r="D42" s="592"/>
-      <c r="E42" s="592"/>
-      <c r="F42" s="597"/>
-      <c r="G42" s="598"/>
-      <c r="H42" s="599"/>
+      <c r="D42" s="602"/>
+      <c r="E42" s="602"/>
+      <c r="F42" s="607"/>
+      <c r="G42" s="608"/>
+      <c r="H42" s="609"/>
       <c r="X42" s="32"/>
     </row>
     <row r="43" spans="1:24">
@@ -40090,12 +40093,29 @@
       <c r="H46" s="51"/>
     </row>
     <row r="47" spans="1:24">
-      <c r="F47" s="586"/>
-      <c r="G47" s="586"/>
-      <c r="H47" s="586"/>
+      <c r="F47" s="597"/>
+      <c r="G47" s="597"/>
+      <c r="H47" s="597"/>
     </row>
   </sheetData>
   <mergeCells count="33">
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C12:H12"/>
+    <mergeCell ref="F47:H47"/>
+    <mergeCell ref="A31:H31"/>
+    <mergeCell ref="A21:H21"/>
+    <mergeCell ref="A18:H18"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="C36:H41"/>
+    <mergeCell ref="C42:E42"/>
+    <mergeCell ref="F42:H42"/>
+    <mergeCell ref="A34:H34"/>
+    <mergeCell ref="A11:H11"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="G32:H32"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="C9:D9"/>
     <mergeCell ref="Z1:AB1"/>
     <mergeCell ref="AC1:AE1"/>
     <mergeCell ref="AF1:AG1"/>
@@ -40112,23 +40132,6 @@
     <mergeCell ref="E6:F6"/>
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="C15:D15"/>
-    <mergeCell ref="A11:H11"/>
-    <mergeCell ref="A5:H5"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="G32:H32"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C12:H12"/>
-    <mergeCell ref="F47:H47"/>
-    <mergeCell ref="A31:H31"/>
-    <mergeCell ref="A21:H21"/>
-    <mergeCell ref="A18:H18"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="C36:H41"/>
-    <mergeCell ref="C42:E42"/>
-    <mergeCell ref="F42:H42"/>
-    <mergeCell ref="A34:H34"/>
   </mergeCells>
   <dataValidations count="7">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D19:D20 B40:B41" xr:uid="{00000000-0002-0000-0300-000000000000}">
@@ -40174,51 +40177,51 @@
     <col min="6" max="6" width="23.33203125" customWidth="1"/>
     <col min="7" max="7" width="18" customWidth="1"/>
     <col min="8" max="8" width="17.46484375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="0.33203125" style="305" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="10.796875" style="305" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="13" style="305" customWidth="1"/>
+    <col min="10" max="10" width="10.796875" style="305" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="176"/>
-      <c r="D1" s="615" t="s">
+      <c r="D1" s="624" t="s">
         <v>315</v>
       </c>
-      <c r="E1" s="579">
+      <c r="E1" s="507">
         <f>'Nota de venta'!H1</f>
         <v>0</v>
       </c>
-      <c r="F1" s="526"/>
+      <c r="F1" s="573"/>
     </row>
     <row r="2" spans="1:11" ht="14.65" thickBot="1">
       <c r="A2" s="176"/>
-      <c r="D2" s="615"/>
-      <c r="E2" s="616"/>
-      <c r="F2" s="528"/>
+      <c r="D2" s="624"/>
+      <c r="E2" s="625"/>
+      <c r="F2" s="575"/>
     </row>
     <row r="3" spans="1:11" ht="14.65" thickBot="1">
       <c r="A3" s="176"/>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="176"/>
-      <c r="D4" s="617">
+      <c r="D4" s="626">
         <f>'Nota de venta'!C112</f>
         <v>0</v>
       </c>
-      <c r="E4" s="618"/>
-      <c r="F4" s="619"/>
+      <c r="E4" s="627"/>
+      <c r="F4" s="628"/>
     </row>
     <row r="5" spans="1:11" ht="14.65" thickBot="1">
-      <c r="D5" s="620"/>
-      <c r="E5" s="621"/>
-      <c r="F5" s="622"/>
+      <c r="D5" s="629"/>
+      <c r="E5" s="630"/>
+      <c r="F5" s="631"/>
     </row>
     <row r="6" spans="1:11" ht="28.9" customHeight="1" thickBot="1">
-      <c r="D6" s="633">
+      <c r="D6" s="632">
         <f>'Nota de venta'!C6</f>
         <v>0</v>
       </c>
-      <c r="E6" s="634"/>
-      <c r="F6" s="635"/>
+      <c r="E6" s="633"/>
+      <c r="F6" s="634"/>
     </row>
     <row r="7" spans="1:11" ht="21.4" thickBot="1">
       <c r="G7" s="273" t="s">
@@ -40265,19 +40268,19 @@
       </c>
     </row>
     <row r="10" spans="1:11" ht="31.05" customHeight="1">
-      <c r="A10" s="623">
+      <c r="A10" s="614">
         <f>+'NV CAJAS (BL)'!D16</f>
         <v>0</v>
       </c>
-      <c r="B10" s="611">
+      <c r="B10" s="610">
         <f>+'NV CAJAS (BL)'!C16</f>
         <v>0</v>
       </c>
-      <c r="C10" s="627">
+      <c r="C10" s="618">
         <f>'Nota de venta'!E10</f>
         <v>0</v>
       </c>
-      <c r="D10" s="630">
+      <c r="D10" s="621">
         <f>'Nota de venta'!F10</f>
         <v>0</v>
       </c>
@@ -40304,10 +40307,10 @@
       </c>
     </row>
     <row r="11" spans="1:11" ht="27" customHeight="1">
-      <c r="A11" s="624"/>
-      <c r="B11" s="626"/>
-      <c r="C11" s="628"/>
-      <c r="D11" s="631"/>
+      <c r="A11" s="615"/>
+      <c r="B11" s="617"/>
+      <c r="C11" s="619"/>
+      <c r="D11" s="622"/>
       <c r="E11" s="289" t="s">
         <v>243</v>
       </c>
@@ -40332,10 +40335,10 @@
       </c>
     </row>
     <row r="12" spans="1:11" ht="38" customHeight="1" thickBot="1">
-      <c r="A12" s="625"/>
-      <c r="B12" s="613"/>
-      <c r="C12" s="629"/>
-      <c r="D12" s="632"/>
+      <c r="A12" s="616"/>
+      <c r="B12" s="612"/>
+      <c r="C12" s="620"/>
+      <c r="D12" s="623"/>
       <c r="E12" s="289" t="s">
         <v>306</v>
       </c>
@@ -40356,9 +40359,9 @@
       <c r="A13" s="293" t="s">
         <v>318</v>
       </c>
-      <c r="B13" s="611"/>
-      <c r="C13" s="612"/>
-      <c r="D13" s="526"/>
+      <c r="B13" s="610"/>
+      <c r="C13" s="611"/>
+      <c r="D13" s="573"/>
       <c r="E13" s="289" t="s">
         <v>307</v>
       </c>
@@ -40377,9 +40380,9 @@
     </row>
     <row r="14" spans="1:11" ht="35" customHeight="1" thickBot="1">
       <c r="A14" s="284"/>
-      <c r="B14" s="613"/>
-      <c r="C14" s="614"/>
-      <c r="D14" s="528"/>
+      <c r="B14" s="612"/>
+      <c r="C14" s="613"/>
+      <c r="D14" s="575"/>
       <c r="E14" s="294" t="s">
         <v>191</v>
       </c>
@@ -40400,19 +40403,19 @@
       </c>
     </row>
     <row r="15" spans="1:11" ht="26" customHeight="1">
-      <c r="A15" s="623">
+      <c r="A15" s="614">
         <f>+'NV CAJAS (BL)'!D17</f>
         <v>0</v>
       </c>
-      <c r="B15" s="611">
+      <c r="B15" s="610">
         <f>+'NV CAJAS (BL)'!C17</f>
         <v>0</v>
       </c>
-      <c r="C15" s="627">
+      <c r="C15" s="618">
         <f>'Nota de venta'!E11</f>
         <v>0</v>
       </c>
-      <c r="D15" s="630">
+      <c r="D15" s="621">
         <f>'Nota de venta'!F11</f>
         <v>0</v>
       </c>
@@ -40439,10 +40442,10 @@
       </c>
     </row>
     <row r="16" spans="1:11" ht="26" customHeight="1">
-      <c r="A16" s="624"/>
-      <c r="B16" s="626"/>
-      <c r="C16" s="628"/>
-      <c r="D16" s="631"/>
+      <c r="A16" s="615"/>
+      <c r="B16" s="617"/>
+      <c r="C16" s="619"/>
+      <c r="D16" s="622"/>
       <c r="E16" s="289" t="s">
         <v>243</v>
       </c>
@@ -40467,10 +40470,10 @@
       </c>
     </row>
     <row r="17" spans="1:11" ht="44" customHeight="1" thickBot="1">
-      <c r="A17" s="625"/>
-      <c r="B17" s="613"/>
-      <c r="C17" s="629"/>
-      <c r="D17" s="632"/>
+      <c r="A17" s="616"/>
+      <c r="B17" s="612"/>
+      <c r="C17" s="620"/>
+      <c r="D17" s="623"/>
       <c r="E17" s="289" t="s">
         <v>306</v>
       </c>
@@ -40491,9 +40494,9 @@
       <c r="A18" s="293" t="s">
         <v>318</v>
       </c>
-      <c r="B18" s="611"/>
-      <c r="C18" s="612"/>
-      <c r="D18" s="526"/>
+      <c r="B18" s="610"/>
+      <c r="C18" s="611"/>
+      <c r="D18" s="573"/>
       <c r="E18" s="289" t="s">
         <v>307</v>
       </c>
@@ -40512,9 +40515,9 @@
     </row>
     <row r="19" spans="1:11" ht="43.05" customHeight="1" thickBot="1">
       <c r="A19" s="284"/>
-      <c r="B19" s="613"/>
-      <c r="C19" s="614"/>
-      <c r="D19" s="528"/>
+      <c r="B19" s="612"/>
+      <c r="C19" s="613"/>
+      <c r="D19" s="575"/>
       <c r="E19" s="294" t="s">
         <v>191</v>
       </c>
@@ -40535,19 +40538,19 @@
       </c>
     </row>
     <row r="20" spans="1:11" ht="28.05" customHeight="1">
-      <c r="A20" s="623">
+      <c r="A20" s="614">
         <f>+'NV CAJAS (BL)'!D18</f>
         <v>0</v>
       </c>
-      <c r="B20" s="611">
+      <c r="B20" s="610">
         <f>+'NV CAJAS (BL)'!C18</f>
         <v>0</v>
       </c>
-      <c r="C20" s="627">
+      <c r="C20" s="618">
         <f>'Nota de venta'!E12</f>
         <v>0</v>
       </c>
-      <c r="D20" s="630">
+      <c r="D20" s="621">
         <f>'Nota de venta'!F12</f>
         <v>0</v>
       </c>
@@ -40574,10 +40577,10 @@
       </c>
     </row>
     <row r="21" spans="1:11" ht="29" customHeight="1">
-      <c r="A21" s="624"/>
-      <c r="B21" s="626"/>
-      <c r="C21" s="628"/>
-      <c r="D21" s="631"/>
+      <c r="A21" s="615"/>
+      <c r="B21" s="617"/>
+      <c r="C21" s="619"/>
+      <c r="D21" s="622"/>
       <c r="E21" s="277" t="s">
         <v>243</v>
       </c>
@@ -40602,10 +40605,10 @@
       </c>
     </row>
     <row r="22" spans="1:11" ht="32" customHeight="1" thickBot="1">
-      <c r="A22" s="625"/>
-      <c r="B22" s="613"/>
-      <c r="C22" s="629"/>
-      <c r="D22" s="632"/>
+      <c r="A22" s="616"/>
+      <c r="B22" s="612"/>
+      <c r="C22" s="620"/>
+      <c r="D22" s="623"/>
       <c r="E22" s="277" t="s">
         <v>306</v>
       </c>
@@ -40626,9 +40629,9 @@
       <c r="A23" s="293" t="s">
         <v>318</v>
       </c>
-      <c r="B23" s="611"/>
-      <c r="C23" s="612"/>
-      <c r="D23" s="526"/>
+      <c r="B23" s="610"/>
+      <c r="C23" s="611"/>
+      <c r="D23" s="573"/>
       <c r="E23" s="277" t="s">
         <v>307</v>
       </c>
@@ -40647,9 +40650,9 @@
     </row>
     <row r="24" spans="1:11" ht="39" customHeight="1" thickBot="1">
       <c r="A24" s="284"/>
-      <c r="B24" s="613"/>
-      <c r="C24" s="614"/>
-      <c r="D24" s="528"/>
+      <c r="B24" s="612"/>
+      <c r="C24" s="613"/>
+      <c r="D24" s="575"/>
       <c r="E24" s="278" t="s">
         <v>191</v>
       </c>
@@ -40670,19 +40673,19 @@
       </c>
     </row>
     <row r="25" spans="1:11" ht="25.05" customHeight="1">
-      <c r="A25" s="623">
+      <c r="A25" s="614">
         <f>+'NV CAJAS (BL)'!D19</f>
         <v>0</v>
       </c>
-      <c r="B25" s="611">
+      <c r="B25" s="610">
         <f>+'NV CAJAS (BL)'!C19</f>
         <v>0</v>
       </c>
-      <c r="C25" s="627">
+      <c r="C25" s="618">
         <f>'Nota de venta'!E13</f>
         <v>0</v>
       </c>
-      <c r="D25" s="630">
+      <c r="D25" s="621">
         <f>'Nota de venta'!F13</f>
         <v>0</v>
       </c>
@@ -40709,10 +40712,10 @@
       </c>
     </row>
     <row r="26" spans="1:11" ht="25.05" customHeight="1">
-      <c r="A26" s="624"/>
-      <c r="B26" s="626"/>
-      <c r="C26" s="628"/>
-      <c r="D26" s="631"/>
+      <c r="A26" s="615"/>
+      <c r="B26" s="617"/>
+      <c r="C26" s="619"/>
+      <c r="D26" s="622"/>
       <c r="E26" s="277" t="s">
         <v>243</v>
       </c>
@@ -40737,10 +40740,10 @@
       </c>
     </row>
     <row r="27" spans="1:11" ht="29" customHeight="1" thickBot="1">
-      <c r="A27" s="625"/>
-      <c r="B27" s="613"/>
-      <c r="C27" s="629"/>
-      <c r="D27" s="632"/>
+      <c r="A27" s="616"/>
+      <c r="B27" s="612"/>
+      <c r="C27" s="620"/>
+      <c r="D27" s="623"/>
       <c r="E27" s="277" t="s">
         <v>306</v>
       </c>
@@ -40761,9 +40764,9 @@
       <c r="A28" s="293" t="s">
         <v>318</v>
       </c>
-      <c r="B28" s="611"/>
-      <c r="C28" s="612"/>
-      <c r="D28" s="526"/>
+      <c r="B28" s="610"/>
+      <c r="C28" s="611"/>
+      <c r="D28" s="573"/>
       <c r="E28" s="277" t="s">
         <v>307</v>
       </c>
@@ -40782,9 +40785,9 @@
     </row>
     <row r="29" spans="1:11" ht="41" customHeight="1" thickBot="1">
       <c r="A29" s="284"/>
-      <c r="B29" s="613"/>
-      <c r="C29" s="614"/>
-      <c r="D29" s="528"/>
+      <c r="B29" s="612"/>
+      <c r="C29" s="613"/>
+      <c r="D29" s="575"/>
       <c r="E29" s="278" t="s">
         <v>191</v>
       </c>
@@ -40806,16 +40809,6 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="B28:D29"/>
-    <mergeCell ref="A20:A22"/>
-    <mergeCell ref="B20:B22"/>
-    <mergeCell ref="C20:C22"/>
-    <mergeCell ref="D20:D22"/>
-    <mergeCell ref="B23:D24"/>
-    <mergeCell ref="A25:A27"/>
-    <mergeCell ref="B25:B27"/>
-    <mergeCell ref="C25:C27"/>
-    <mergeCell ref="D25:D27"/>
     <mergeCell ref="B18:D19"/>
     <mergeCell ref="D1:D2"/>
     <mergeCell ref="E1:F2"/>
@@ -40830,6 +40823,16 @@
     <mergeCell ref="C15:C17"/>
     <mergeCell ref="D15:D17"/>
     <mergeCell ref="D6:F6"/>
+    <mergeCell ref="B28:D29"/>
+    <mergeCell ref="A20:A22"/>
+    <mergeCell ref="B20:B22"/>
+    <mergeCell ref="C20:C22"/>
+    <mergeCell ref="D20:D22"/>
+    <mergeCell ref="B23:D24"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="B25:B27"/>
+    <mergeCell ref="C25:C27"/>
+    <mergeCell ref="D25:D27"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="70" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -40895,10 +40898,10 @@
     <col min="52" max="52" width="6.796875" style="59" customWidth="1"/>
     <col min="53" max="54" width="23.46484375" style="59" customWidth="1"/>
     <col min="55" max="55" width="5.33203125" style="59" customWidth="1"/>
-    <col min="56" max="56" width="9.33203125" style="59" customWidth="1"/>
-    <col min="57" max="57" width="15" style="59" customWidth="1"/>
+    <col min="56" max="56" width="13.19921875" style="59" customWidth="1"/>
+    <col min="57" max="57" width="20.19921875" style="59" customWidth="1"/>
     <col min="58" max="58" width="7.33203125" style="59" customWidth="1"/>
-    <col min="59" max="59" width="10.46484375" style="59" customWidth="1"/>
+    <col min="59" max="59" width="12.33203125" style="59" hidden="1" customWidth="1"/>
     <col min="60" max="60" width="5.6640625" style="59" customWidth="1"/>
     <col min="61" max="61" width="10" style="59" customWidth="1"/>
     <col min="62" max="65" width="15.1328125" style="59" customWidth="1"/>
@@ -41082,8 +41085,8 @@
       <c r="D5" s="103"/>
       <c r="E5" s="103"/>
       <c r="H5" s="64"/>
-      <c r="I5" s="484"/>
-      <c r="J5" s="484"/>
+      <c r="I5" s="544"/>
+      <c r="J5" s="544"/>
       <c r="M5" s="104"/>
       <c r="R5" s="59"/>
       <c r="Z5" s="59"/>
@@ -41179,18 +41182,18 @@
       <c r="BN6" s="59"/>
     </row>
     <row r="7" spans="1:93" ht="38" hidden="1" customHeight="1" thickBot="1">
-      <c r="B7" s="640" t="s">
+      <c r="B7" s="639" t="s">
         <v>45</v>
       </c>
-      <c r="C7" s="641"/>
-      <c r="D7" s="641"/>
-      <c r="E7" s="641"/>
-      <c r="F7" s="641"/>
-      <c r="G7" s="641"/>
-      <c r="H7" s="641"/>
-      <c r="I7" s="641"/>
-      <c r="J7" s="641"/>
-      <c r="K7" s="642"/>
+      <c r="C7" s="640"/>
+      <c r="D7" s="640"/>
+      <c r="E7" s="640"/>
+      <c r="F7" s="640"/>
+      <c r="G7" s="640"/>
+      <c r="H7" s="640"/>
+      <c r="I7" s="640"/>
+      <c r="J7" s="640"/>
+      <c r="K7" s="641"/>
       <c r="L7" s="66"/>
       <c r="M7" s="66"/>
       <c r="R7" s="59"/>
@@ -41240,20 +41243,20 @@
       <c r="B8" s="62" t="s">
         <v>55</v>
       </c>
-      <c r="C8" s="652">
+      <c r="C8" s="651">
         <f>'Nota de venta'!C5</f>
         <v>0</v>
       </c>
-      <c r="D8" s="653"/>
-      <c r="E8" s="653"/>
-      <c r="F8" s="654"/>
+      <c r="D8" s="652"/>
+      <c r="E8" s="652"/>
+      <c r="F8" s="653"/>
       <c r="G8" s="167"/>
       <c r="H8" s="62" t="s">
         <v>124</v>
       </c>
-      <c r="I8" s="643"/>
-      <c r="J8" s="644"/>
-      <c r="K8" s="645"/>
+      <c r="I8" s="642"/>
+      <c r="J8" s="643"/>
+      <c r="K8" s="644"/>
       <c r="L8" s="85"/>
       <c r="M8" s="85"/>
       <c r="R8" s="59"/>
@@ -41286,18 +41289,18 @@
       <c r="B9" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="652">
+      <c r="C9" s="651">
         <f>'Nota de venta'!C6</f>
         <v>0</v>
       </c>
-      <c r="D9" s="653"/>
-      <c r="E9" s="653"/>
-      <c r="F9" s="654"/>
+      <c r="D9" s="652"/>
+      <c r="E9" s="652"/>
+      <c r="F9" s="653"/>
       <c r="G9" s="167"/>
       <c r="H9" s="89"/>
-      <c r="I9" s="646"/>
-      <c r="J9" s="647"/>
-      <c r="K9" s="648"/>
+      <c r="I9" s="645"/>
+      <c r="J9" s="646"/>
+      <c r="K9" s="647"/>
       <c r="L9" s="90"/>
       <c r="M9" s="90"/>
       <c r="R9" s="59"/>
@@ -41365,18 +41368,18 @@
     <row r="12" spans="1:93" ht="16.149999999999999" thickBot="1"/>
     <row r="13" spans="1:93" ht="40.5" customHeight="1" thickBot="1">
       <c r="C13" s="102"/>
-      <c r="D13" s="649" t="s">
+      <c r="D13" s="648" t="s">
         <v>155</v>
       </c>
-      <c r="E13" s="650"/>
-      <c r="F13" s="650"/>
-      <c r="G13" s="650"/>
-      <c r="H13" s="650"/>
-      <c r="I13" s="650"/>
-      <c r="J13" s="650"/>
-      <c r="K13" s="650"/>
-      <c r="L13" s="650"/>
-      <c r="M13" s="651"/>
+      <c r="E13" s="649"/>
+      <c r="F13" s="649"/>
+      <c r="G13" s="649"/>
+      <c r="H13" s="649"/>
+      <c r="I13" s="649"/>
+      <c r="J13" s="649"/>
+      <c r="K13" s="649"/>
+      <c r="L13" s="649"/>
+      <c r="M13" s="650"/>
       <c r="N13" s="66"/>
       <c r="P13" s="69"/>
       <c r="Q13" s="69"/>
@@ -41442,7 +41445,9 @@
         <v>127</v>
       </c>
       <c r="BR13" s="205"/>
-      <c r="BS13" s="474"/>
+      <c r="BS13" s="654" t="s">
+        <v>635</v>
+      </c>
       <c r="BT13" s="188" t="s">
         <v>270</v>
       </c>
@@ -41480,15 +41485,15 @@
       </c>
       <c r="D14" s="70"/>
       <c r="E14" s="70"/>
-      <c r="F14" s="636" t="s">
+      <c r="F14" s="635" t="s">
         <v>117</v>
       </c>
-      <c r="G14" s="637"/>
-      <c r="H14" s="558"/>
-      <c r="I14" s="558"/>
-      <c r="J14" s="558"/>
-      <c r="K14" s="558"/>
-      <c r="L14" s="638"/>
+      <c r="G14" s="636"/>
+      <c r="H14" s="482"/>
+      <c r="I14" s="482"/>
+      <c r="J14" s="482"/>
+      <c r="K14" s="482"/>
+      <c r="L14" s="637"/>
       <c r="M14" s="84"/>
       <c r="O14" s="93"/>
       <c r="AM14" s="68"/>
@@ -41511,6 +41516,15 @@
         <v>135</v>
       </c>
       <c r="BB14" s="107"/>
+      <c r="BE14" s="215" t="s">
+        <v>280</v>
+      </c>
+      <c r="BF14" s="216" t="s">
+        <v>240</v>
+      </c>
+      <c r="BH14" s="218" t="s">
+        <v>172</v>
+      </c>
       <c r="BL14" s="210" t="s">
         <v>309</v>
       </c>
@@ -41526,7 +41540,7 @@
         <v>102</v>
       </c>
       <c r="BR14" s="206"/>
-      <c r="BS14" s="475">
+      <c r="BS14" s="474">
         <v>600</v>
       </c>
       <c r="BT14" s="192" t="s">
@@ -41566,7 +41580,7 @@
         <v>214</v>
       </c>
       <c r="C15" s="261" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D15" s="262" t="s">
         <v>6</v>
@@ -41578,7 +41592,7 @@
         <v>232</v>
       </c>
       <c r="G15" s="157" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="H15" s="263" t="s">
         <v>200</v>
@@ -41629,7 +41643,7 @@
         <v>191</v>
       </c>
       <c r="X15" s="265" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="Y15" s="262" t="s">
         <v>144</v>
@@ -41718,7 +41732,7 @@
         <v>5000</v>
       </c>
       <c r="BR15" s="206"/>
-      <c r="BS15" s="475">
+      <c r="BS15" s="474">
         <v>450</v>
       </c>
       <c r="BT15" s="192" t="s">
@@ -41955,7 +41969,7 @@
         <v>14040.000000000002</v>
       </c>
       <c r="BR16" s="206"/>
-      <c r="BS16" s="475">
+      <c r="BS16" s="474">
         <v>350</v>
       </c>
       <c r="BT16" s="192" t="s">
@@ -42151,7 +42165,7 @@
         <v>331</v>
       </c>
       <c r="BE17" s="221" t="s">
-        <v>332</v>
+        <v>636</v>
       </c>
       <c r="BF17" s="200">
         <v>0.6</v>
@@ -42184,7 +42198,7 @@
       <c r="BO17"/>
       <c r="BQ17" s="187"/>
       <c r="BR17" s="206"/>
-      <c r="BS17" s="475">
+      <c r="BS17" s="474">
         <v>200</v>
       </c>
       <c r="BT17" s="194" t="s">
@@ -42419,7 +42433,7 @@
         <v>0</v>
       </c>
       <c r="BR18" s="206"/>
-      <c r="BS18" s="475">
+      <c r="BS18" s="474">
         <v>150</v>
       </c>
       <c r="BT18" s="194" t="s">
@@ -43078,9 +43092,7 @@
       <c r="BH21" s="199">
         <v>60</v>
       </c>
-      <c r="BI21" s="202">
-        <v>1</v>
-      </c>
+      <c r="BI21" s="202"/>
       <c r="BJ21" s="201">
         <v>26752</v>
       </c>
@@ -43290,15 +43302,17 @@
         <v>296</v>
       </c>
       <c r="BE22" s="223" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="BF22" s="203">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="BG22" s="201">
         <v>25000</v>
       </c>
-      <c r="BH22" s="199"/>
+      <c r="BH22" s="199">
+        <v>120</v>
+      </c>
       <c r="BI22" s="202"/>
       <c r="BJ22" s="201"/>
       <c r="BK22" s="222" t="s">
@@ -43534,13 +43548,13 @@
       <c r="BR23" s="68"/>
       <c r="BS23" s="68"/>
       <c r="BT23" s="59" t="s">
-        <v>635</v>
-      </c>
-      <c r="BU23" s="476">
+        <v>634</v>
+      </c>
+      <c r="BU23" s="475">
         <f>BU16*2</f>
         <v>80748</v>
       </c>
-      <c r="BV23" s="476">
+      <c r="BV23" s="475">
         <f>BV16*2</f>
         <v>44860</v>
       </c>
@@ -43626,10 +43640,10 @@
       <c r="BB24"/>
       <c r="BC24" s="68"/>
       <c r="BD24" s="59" t="s">
+        <v>332</v>
+      </c>
+      <c r="BE24" s="59" t="s">
         <v>333</v>
-      </c>
-      <c r="BE24" s="59" t="s">
-        <v>334</v>
       </c>
       <c r="BF24" s="59">
         <v>0.45</v>
@@ -43648,7 +43662,7 @@
         <v>16244</v>
       </c>
       <c r="BK24" s="59" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="BL24" s="210"/>
       <c r="BM24" s="107" t="s">
@@ -44963,9 +44977,9 @@
       <c r="AP36" s="108"/>
       <c r="AQ36" s="123"/>
       <c r="AR36" s="68"/>
-      <c r="AS36" s="639"/>
-      <c r="AT36" s="639"/>
-      <c r="AU36" s="639"/>
+      <c r="AS36" s="638"/>
+      <c r="AT36" s="638"/>
+      <c r="AU36" s="638"/>
       <c r="AV36" s="108"/>
       <c r="AW36" s="123"/>
       <c r="AX36" s="68"/>
@@ -46395,33 +46409,33 @@
   <sheetData>
     <row r="1" spans="1:8" s="107" customFormat="1" ht="39" customHeight="1">
       <c r="A1" s="383" t="s">
+        <v>418</v>
+      </c>
+      <c r="B1" s="383" t="s">
         <v>419</v>
       </c>
-      <c r="B1" s="383" t="s">
+      <c r="C1" s="383" t="s">
         <v>420</v>
       </c>
-      <c r="C1" s="383" t="s">
+      <c r="D1" s="383" t="s">
         <v>421</v>
       </c>
-      <c r="D1" s="383" t="s">
+      <c r="E1" s="383" t="s">
         <v>422</v>
       </c>
-      <c r="E1" s="383" t="s">
+      <c r="F1" s="383" t="s">
         <v>423</v>
       </c>
-      <c r="F1" s="383" t="s">
+      <c r="G1" s="383" t="s">
         <v>424</v>
       </c>
-      <c r="G1" s="383" t="s">
+      <c r="H1" s="383" t="s">
         <v>425</v>
-      </c>
-      <c r="H1" s="383" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="124" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B2" s="200"/>
       <c r="C2" s="200"/>
@@ -46435,7 +46449,7 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="124" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B3" s="200"/>
       <c r="C3" s="200"/>
@@ -46449,7 +46463,7 @@
     </row>
     <row r="4" spans="1:8" ht="28.5">
       <c r="A4" s="124" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B4" s="200">
         <v>234</v>
@@ -46458,10 +46472,10 @@
         <v>154</v>
       </c>
       <c r="D4" s="124" t="s">
+        <v>426</v>
+      </c>
+      <c r="E4" s="124" t="s">
         <v>427</v>
-      </c>
-      <c r="E4" s="124" t="s">
-        <v>428</v>
       </c>
       <c r="F4" s="151">
         <v>5200</v>
@@ -46471,7 +46485,7 @@
     </row>
     <row r="5" spans="1:8" ht="28.5">
       <c r="A5" s="124" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B5" s="200">
         <v>304</v>
@@ -46480,10 +46494,10 @@
         <v>204</v>
       </c>
       <c r="D5" s="124" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E5" s="124" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F5" s="151">
         <v>10300</v>
@@ -46493,7 +46507,7 @@
     </row>
     <row r="6" spans="1:8" ht="28.5">
       <c r="A6" s="124" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B6" s="200">
         <v>154</v>
@@ -46502,10 +46516,10 @@
         <v>105</v>
       </c>
       <c r="D6" s="124" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E6" s="124" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F6" s="151">
         <v>4000</v>
@@ -46515,15 +46529,15 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="152" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B7" s="200"/>
       <c r="C7" s="200"/>
       <c r="D7" s="124" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E7" s="124" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F7" s="151"/>
       <c r="G7" s="151">
@@ -46533,15 +46547,15 @@
     </row>
     <row r="8" spans="1:8" ht="31.5">
       <c r="A8" s="326" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B8" s="200"/>
       <c r="C8" s="200"/>
       <c r="D8" s="124" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E8" s="124" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F8" s="151"/>
       <c r="G8" s="151">
@@ -46551,15 +46565,15 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="124" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B9" s="200"/>
       <c r="C9" s="200"/>
       <c r="D9" s="124" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E9" s="124" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F9" s="151"/>
       <c r="G9" s="151">
@@ -46569,15 +46583,15 @@
     </row>
     <row r="10" spans="1:8" ht="28.5">
       <c r="A10" s="124" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B10" s="200"/>
       <c r="C10" s="200"/>
       <c r="D10" s="124" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E10" s="124" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F10" s="151">
         <v>0</v>
@@ -46591,15 +46605,15 @@
     </row>
     <row r="11" spans="1:8" ht="28.5">
       <c r="A11" s="124" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B11" s="200"/>
       <c r="C11" s="200"/>
       <c r="D11" s="124" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E11" s="124" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F11" s="151">
         <v>0</v>
@@ -46613,7 +46627,7 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="124" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B12" s="200">
         <v>22</v>
@@ -46622,10 +46636,10 @@
         <v>66</v>
       </c>
       <c r="D12" s="124" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E12" s="124" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F12" s="151">
         <v>4100</v>
@@ -46639,7 +46653,7 @@
     </row>
     <row r="13" spans="1:8" ht="28.5">
       <c r="A13" s="124" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B13" s="200">
         <v>22</v>
@@ -46648,10 +46662,10 @@
         <v>35</v>
       </c>
       <c r="D13" s="124" t="s">
+        <v>437</v>
+      </c>
+      <c r="E13" s="124" t="s">
         <v>438</v>
-      </c>
-      <c r="E13" s="124" t="s">
-        <v>439</v>
       </c>
       <c r="F13" s="151">
         <v>3700</v>
@@ -46665,15 +46679,15 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="124" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B14" s="200"/>
       <c r="C14" s="200"/>
       <c r="D14" s="124" t="s">
+        <v>440</v>
+      </c>
+      <c r="E14" s="124" t="s">
         <v>441</v>
-      </c>
-      <c r="E14" s="124" t="s">
-        <v>442</v>
       </c>
       <c r="F14" s="151">
         <v>7000</v>
@@ -46687,15 +46701,15 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="152" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B15" s="200"/>
       <c r="C15" s="200"/>
       <c r="D15" s="124" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E15" s="124" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F15" s="151"/>
       <c r="G15" s="151">
@@ -46705,7 +46719,7 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="124" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B16" s="200">
         <v>20</v>
@@ -46714,10 +46728,10 @@
         <v>50</v>
       </c>
       <c r="D16" s="124" t="s">
+        <v>443</v>
+      </c>
+      <c r="E16" s="124" t="s">
         <v>444</v>
-      </c>
-      <c r="E16" s="124" t="s">
-        <v>445</v>
       </c>
       <c r="F16" s="151">
         <v>3300</v>
@@ -46731,7 +46745,7 @@
     </row>
     <row r="17" spans="1:8" ht="28.5">
       <c r="A17" s="124" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B17" s="200">
         <v>20</v>
@@ -46740,10 +46754,10 @@
         <v>26</v>
       </c>
       <c r="D17" s="124" t="s">
+        <v>446</v>
+      </c>
+      <c r="E17" s="124" t="s">
         <v>447</v>
-      </c>
-      <c r="E17" s="124" t="s">
-        <v>448</v>
       </c>
       <c r="F17" s="151">
         <v>3000</v>
@@ -46757,7 +46771,7 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="124" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B18" s="200">
         <v>20</v>
@@ -46766,10 +46780,10 @@
         <v>25</v>
       </c>
       <c r="D18" s="124" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E18" s="124" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F18" s="151">
         <v>3000</v>
@@ -46783,7 +46797,7 @@
     </row>
     <row r="19" spans="1:8" ht="28.5">
       <c r="A19" s="124" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B19" s="200">
         <v>26</v>
@@ -46792,10 +46806,10 @@
         <v>26</v>
       </c>
       <c r="D19" s="124" t="s">
+        <v>451</v>
+      </c>
+      <c r="E19" s="124" t="s">
         <v>452</v>
-      </c>
-      <c r="E19" s="124" t="s">
-        <v>453</v>
       </c>
       <c r="F19" s="151">
         <v>3000</v>
@@ -46809,7 +46823,7 @@
     </row>
     <row r="20" spans="1:8" ht="28.5">
       <c r="A20" s="124" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B20" s="200">
         <v>232</v>
@@ -46818,10 +46832,10 @@
         <v>232</v>
       </c>
       <c r="D20" s="124" t="s">
+        <v>453</v>
+      </c>
+      <c r="E20" s="124" t="s">
         <v>454</v>
-      </c>
-      <c r="E20" s="124" t="s">
-        <v>455</v>
       </c>
       <c r="F20" s="151">
         <v>8000</v>
@@ -46835,7 +46849,7 @@
     </row>
     <row r="21" spans="1:8" ht="28.5">
       <c r="A21" s="124" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B21" s="200">
         <v>52</v>
@@ -46844,10 +46858,10 @@
         <v>72</v>
       </c>
       <c r="D21" s="124" t="s">
+        <v>456</v>
+      </c>
+      <c r="E21" s="124" t="s">
         <v>457</v>
-      </c>
-      <c r="E21" s="124" t="s">
-        <v>458</v>
       </c>
       <c r="F21" s="151">
         <v>4500</v>
@@ -46861,7 +46875,7 @@
     </row>
     <row r="22" spans="1:8" ht="28.5">
       <c r="A22" s="124" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B22" s="200">
         <v>52</v>
@@ -46870,10 +46884,10 @@
         <v>73</v>
       </c>
       <c r="D22" s="124" t="s">
+        <v>459</v>
+      </c>
+      <c r="E22" s="124" t="s">
         <v>460</v>
-      </c>
-      <c r="E22" s="124" t="s">
-        <v>461</v>
       </c>
       <c r="F22" s="151">
         <v>3500</v>
@@ -46887,7 +46901,7 @@
     </row>
     <row r="23" spans="1:8" ht="28.5">
       <c r="A23" s="124" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B23" s="200">
         <v>52</v>
@@ -46896,10 +46910,10 @@
         <v>92</v>
       </c>
       <c r="D23" s="124" t="s">
+        <v>456</v>
+      </c>
+      <c r="E23" s="124" t="s">
         <v>457</v>
-      </c>
-      <c r="E23" s="124" t="s">
-        <v>458</v>
       </c>
       <c r="F23" s="151">
         <v>5500</v>
@@ -46913,7 +46927,7 @@
     </row>
     <row r="24" spans="1:8" ht="28.5">
       <c r="A24" s="124" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B24" s="200">
         <v>52</v>
@@ -46922,10 +46936,10 @@
         <v>93</v>
       </c>
       <c r="D24" s="124" t="s">
+        <v>463</v>
+      </c>
+      <c r="E24" s="124" t="s">
         <v>464</v>
-      </c>
-      <c r="E24" s="124" t="s">
-        <v>465</v>
       </c>
       <c r="F24" s="151">
         <v>4000</v>
@@ -46939,7 +46953,7 @@
     </row>
     <row r="25" spans="1:8" ht="28.5">
       <c r="A25" s="124" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B25" s="200">
         <v>43</v>
@@ -46948,10 +46962,10 @@
         <v>42</v>
       </c>
       <c r="D25" s="124" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="E25" s="124" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="F25" s="151">
         <v>3500</v>
@@ -46965,7 +46979,7 @@
     </row>
     <row r="26" spans="1:8" ht="28.5">
       <c r="A26" s="124" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B26" s="200">
         <v>43</v>
@@ -46974,10 +46988,10 @@
         <v>42</v>
       </c>
       <c r="D26" s="124" t="s">
+        <v>463</v>
+      </c>
+      <c r="E26" s="124" t="s">
         <v>464</v>
-      </c>
-      <c r="E26" s="124" t="s">
-        <v>465</v>
       </c>
       <c r="F26" s="151">
         <v>3800</v>
@@ -46991,7 +47005,7 @@
     </row>
     <row r="27" spans="1:8" ht="28.5">
       <c r="A27" s="124" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B27" s="200">
         <v>53</v>
@@ -47000,10 +47014,10 @@
         <v>52</v>
       </c>
       <c r="D27" s="124" t="s">
+        <v>463</v>
+      </c>
+      <c r="E27" s="124" t="s">
         <v>464</v>
-      </c>
-      <c r="E27" s="124" t="s">
-        <v>465</v>
       </c>
       <c r="F27" s="151">
         <v>4000</v>
@@ -47017,7 +47031,7 @@
     </row>
     <row r="28" spans="1:8" ht="28.5">
       <c r="A28" s="124" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B28" s="200">
         <v>53</v>
@@ -47026,10 +47040,10 @@
         <v>52</v>
       </c>
       <c r="D28" s="124" t="s">
+        <v>463</v>
+      </c>
+      <c r="E28" s="124" t="s">
         <v>464</v>
-      </c>
-      <c r="E28" s="124" t="s">
-        <v>465</v>
       </c>
       <c r="F28" s="151">
         <v>4200</v>
@@ -47043,15 +47057,15 @@
     </row>
     <row r="29" spans="1:8" ht="28.5">
       <c r="A29" s="124" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B29" s="200"/>
       <c r="C29" s="200"/>
       <c r="D29" s="124" t="s">
+        <v>470</v>
+      </c>
+      <c r="E29" s="124" t="s">
         <v>471</v>
-      </c>
-      <c r="E29" s="124" t="s">
-        <v>472</v>
       </c>
       <c r="F29" s="151">
         <v>20000</v>
@@ -47061,15 +47075,15 @@
     </row>
     <row r="30" spans="1:8" ht="28.5">
       <c r="A30" s="124" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B30" s="200"/>
       <c r="C30" s="200"/>
       <c r="D30" s="124" t="s">
+        <v>472</v>
+      </c>
+      <c r="E30" s="124" t="s">
         <v>473</v>
-      </c>
-      <c r="E30" s="124" t="s">
-        <v>474</v>
       </c>
       <c r="F30" s="151">
         <v>25000</v>
@@ -47079,15 +47093,15 @@
     </row>
     <row r="31" spans="1:8" ht="42.75">
       <c r="A31" s="124" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B31" s="200"/>
       <c r="C31" s="200"/>
       <c r="D31" s="124" t="s">
+        <v>474</v>
+      </c>
+      <c r="E31" s="124" t="s">
         <v>475</v>
-      </c>
-      <c r="E31" s="124" t="s">
-        <v>476</v>
       </c>
       <c r="F31" s="151">
         <v>23000</v>
@@ -47101,15 +47115,15 @@
     </row>
     <row r="32" spans="1:8" ht="42.75">
       <c r="A32" s="124" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B32" s="200"/>
       <c r="C32" s="200"/>
       <c r="D32" s="124" t="s">
+        <v>474</v>
+      </c>
+      <c r="E32" s="124" t="s">
         <v>475</v>
-      </c>
-      <c r="E32" s="124" t="s">
-        <v>476</v>
       </c>
       <c r="F32" s="151">
         <v>23000</v>
@@ -47123,15 +47137,15 @@
     </row>
     <row r="33" spans="1:8" ht="42.75">
       <c r="A33" s="124" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B33" s="200"/>
       <c r="C33" s="200"/>
       <c r="D33" s="124" t="s">
+        <v>474</v>
+      </c>
+      <c r="E33" s="124" t="s">
         <v>475</v>
-      </c>
-      <c r="E33" s="124" t="s">
-        <v>476</v>
       </c>
       <c r="F33" s="151">
         <v>23000</v>
@@ -47145,15 +47159,15 @@
     </row>
     <row r="34" spans="1:8" ht="42.75">
       <c r="A34" s="124" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B34" s="200"/>
       <c r="C34" s="200"/>
       <c r="D34" s="124" t="s">
+        <v>474</v>
+      </c>
+      <c r="E34" s="124" t="s">
         <v>475</v>
-      </c>
-      <c r="E34" s="124" t="s">
-        <v>476</v>
       </c>
       <c r="F34" s="151">
         <v>23000</v>
@@ -47167,15 +47181,15 @@
     </row>
     <row r="35" spans="1:8" ht="28.5">
       <c r="A35" s="124" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B35" s="200"/>
       <c r="C35" s="200"/>
       <c r="D35" s="124" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E35" s="124" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="F35" s="151">
         <v>10000</v>
@@ -47189,15 +47203,15 @@
     </row>
     <row r="36" spans="1:8" ht="42.75">
       <c r="A36" s="124" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B36" s="200"/>
       <c r="C36" s="200"/>
       <c r="D36" s="124" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E36" s="124" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="F36" s="151">
         <v>10000</v>
@@ -47211,15 +47225,15 @@
     </row>
     <row r="37" spans="1:8" ht="57">
       <c r="A37" s="124" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B37" s="200"/>
       <c r="C37" s="200"/>
       <c r="D37" s="124" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E37" s="124" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="F37" s="151">
         <v>10000</v>
@@ -47233,15 +47247,15 @@
     </row>
     <row r="38" spans="1:8" ht="42.75">
       <c r="A38" s="124" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B38" s="200"/>
       <c r="C38" s="200"/>
       <c r="D38" s="124" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E38" s="124" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="F38" s="151">
         <v>10000</v>
@@ -47255,15 +47269,15 @@
     </row>
     <row r="39" spans="1:8" ht="28.5">
       <c r="A39" s="124" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B39" s="200"/>
       <c r="C39" s="200"/>
       <c r="D39" s="124" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E39" s="124" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="F39" s="151">
         <v>15000</v>
@@ -47277,15 +47291,15 @@
     </row>
     <row r="40" spans="1:8" ht="28.5">
       <c r="A40" s="124" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B40" s="200"/>
       <c r="C40" s="200"/>
       <c r="D40" s="124" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E40" s="124" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="F40" s="151">
         <v>16000</v>
@@ -47299,15 +47313,15 @@
     </row>
     <row r="41" spans="1:8" ht="28.5">
       <c r="A41" s="124" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B41" s="200"/>
       <c r="C41" s="200"/>
       <c r="D41" s="124" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E41" s="124" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="F41" s="151">
         <v>12000</v>
@@ -47321,15 +47335,15 @@
     </row>
     <row r="42" spans="1:8" ht="28.5">
       <c r="A42" s="152" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B42" s="384"/>
       <c r="C42" s="384"/>
       <c r="D42" s="124" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E42" s="124" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="F42" s="151">
         <v>18000</v>
@@ -47343,15 +47357,15 @@
     </row>
     <row r="43" spans="1:8" ht="42.75">
       <c r="A43" s="124" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B43" s="200"/>
       <c r="C43" s="200"/>
       <c r="D43" s="124" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E43" s="124" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="F43" s="151">
         <v>23000</v>
@@ -47361,15 +47375,15 @@
     </row>
     <row r="44" spans="1:8" ht="57">
       <c r="A44" s="124" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B44" s="200"/>
       <c r="C44" s="200"/>
       <c r="D44" s="124" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E44" s="124" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="F44" s="151">
         <v>45000</v>
@@ -47383,15 +47397,15 @@
     </row>
     <row r="45" spans="1:8" ht="42.75">
       <c r="A45" s="124" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B45" s="200"/>
       <c r="C45" s="200"/>
       <c r="D45" s="124" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E45" s="124" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="F45" s="151">
         <v>18000</v>
@@ -47405,15 +47419,15 @@
     </row>
     <row r="46" spans="1:8" ht="42.75">
       <c r="A46" s="124" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B46" s="200"/>
       <c r="C46" s="200"/>
       <c r="D46" s="124" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E46" s="124" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="F46" s="151">
         <v>18000</v>
@@ -47427,7 +47441,7 @@
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="124" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B47" s="200">
         <v>150</v>
@@ -47436,10 +47450,10 @@
         <v>150</v>
       </c>
       <c r="D47" s="124" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E47" s="124" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="F47" s="151">
         <v>4000</v>
@@ -47453,7 +47467,7 @@
     </row>
     <row r="48" spans="1:8" ht="28.5">
       <c r="A48" s="124" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B48" s="200">
         <v>212</v>
@@ -47462,10 +47476,10 @@
         <v>3.02</v>
       </c>
       <c r="D48" s="124" t="s">
+        <v>481</v>
+      </c>
+      <c r="E48" s="124" t="s">
         <v>482</v>
-      </c>
-      <c r="E48" s="124" t="s">
-        <v>483</v>
       </c>
       <c r="F48" s="151">
         <v>7000</v>
@@ -47479,7 +47493,7 @@
     </row>
     <row r="49" spans="1:8" ht="28.5">
       <c r="A49" s="124" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B49" s="200">
         <v>232</v>
@@ -47488,10 +47502,10 @@
         <v>79</v>
       </c>
       <c r="D49" s="124" t="s">
+        <v>484</v>
+      </c>
+      <c r="E49" s="124" t="s">
         <v>485</v>
-      </c>
-      <c r="E49" s="124" t="s">
-        <v>486</v>
       </c>
       <c r="F49" s="151">
         <v>10000</v>
@@ -47505,15 +47519,15 @@
     </row>
     <row r="50" spans="1:8" ht="28.5">
       <c r="A50" s="124" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B50" s="200"/>
       <c r="C50" s="200"/>
       <c r="D50" s="124" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="E50" s="124" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="F50" s="151">
         <v>0</v>
@@ -47527,7 +47541,7 @@
     </row>
     <row r="51" spans="1:8" ht="28.5">
       <c r="A51" s="124" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B51" s="200">
         <v>232</v>
@@ -47536,10 +47550,10 @@
         <v>254</v>
       </c>
       <c r="D51" s="124" t="s">
+        <v>484</v>
+      </c>
+      <c r="E51" s="124" t="s">
         <v>485</v>
-      </c>
-      <c r="E51" s="124" t="s">
-        <v>486</v>
       </c>
       <c r="F51" s="151">
         <v>15000</v>
@@ -47553,15 +47567,15 @@
     </row>
     <row r="52" spans="1:8" ht="28.5">
       <c r="A52" s="124" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B52" s="200"/>
       <c r="C52" s="200"/>
       <c r="D52" s="124" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="E52" s="124" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="F52" s="151"/>
       <c r="G52" s="151">
@@ -47573,7 +47587,7 @@
     </row>
     <row r="53" spans="1:8" ht="28.5">
       <c r="A53" s="124" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B53" s="200">
         <v>232</v>
@@ -47582,10 +47596,10 @@
         <v>234</v>
       </c>
       <c r="D53" s="124" t="s">
+        <v>484</v>
+      </c>
+      <c r="E53" s="124" t="s">
         <v>485</v>
-      </c>
-      <c r="E53" s="124" t="s">
-        <v>486</v>
       </c>
       <c r="F53" s="151">
         <v>18000</v>
@@ -47599,15 +47613,15 @@
     </row>
     <row r="54" spans="1:8" ht="28.5">
       <c r="A54" s="124" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B54" s="200"/>
       <c r="C54" s="200"/>
       <c r="D54" s="124" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="E54" s="124" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="F54" s="151">
         <v>0</v>
@@ -47621,7 +47635,7 @@
     </row>
     <row r="55" spans="1:8" ht="28.5">
       <c r="A55" s="124" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B55" s="200">
         <v>232</v>
@@ -47630,10 +47644,10 @@
         <v>304</v>
       </c>
       <c r="D55" s="124" t="s">
+        <v>484</v>
+      </c>
+      <c r="E55" s="124" t="s">
         <v>485</v>
-      </c>
-      <c r="E55" s="124" t="s">
-        <v>486</v>
       </c>
       <c r="F55" s="151">
         <v>20000</v>
@@ -47647,15 +47661,15 @@
     </row>
     <row r="56" spans="1:8" ht="28.5">
       <c r="A56" s="124" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B56" s="200"/>
       <c r="C56" s="200"/>
       <c r="D56" s="124" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="E56" s="124" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="F56" s="151">
         <v>0</v>
@@ -47669,7 +47683,7 @@
     </row>
     <row r="57" spans="1:8" ht="28.5">
       <c r="A57" s="124" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B57" s="200">
         <v>232</v>
@@ -47678,10 +47692,10 @@
         <v>379</v>
       </c>
       <c r="D57" s="124" t="s">
+        <v>484</v>
+      </c>
+      <c r="E57" s="124" t="s">
         <v>485</v>
-      </c>
-      <c r="E57" s="124" t="s">
-        <v>486</v>
       </c>
       <c r="F57" s="151">
         <v>23000</v>
@@ -47695,15 +47709,15 @@
     </row>
     <row r="58" spans="1:8" ht="28.5">
       <c r="A58" s="124" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B58" s="200"/>
       <c r="C58" s="200"/>
       <c r="D58" s="124" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="E58" s="124" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="F58" s="151">
         <v>0</v>
@@ -47717,7 +47731,7 @@
     </row>
     <row r="59" spans="1:8" ht="28.5">
       <c r="A59" s="124" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B59" s="200">
         <v>232</v>
@@ -47726,10 +47740,10 @@
         <v>454</v>
       </c>
       <c r="D59" s="124" t="s">
+        <v>484</v>
+      </c>
+      <c r="E59" s="124" t="s">
         <v>485</v>
-      </c>
-      <c r="E59" s="124" t="s">
-        <v>486</v>
       </c>
       <c r="F59" s="151">
         <v>25000</v>
@@ -47743,15 +47757,15 @@
     </row>
     <row r="60" spans="1:8" ht="28.5">
       <c r="A60" s="124" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B60" s="200"/>
       <c r="C60" s="200"/>
       <c r="D60" s="124" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="E60" s="124" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="F60" s="151">
         <v>0</v>
@@ -47765,7 +47779,7 @@
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="124" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B61" s="200">
         <v>104</v>
@@ -47774,10 +47788,10 @@
         <v>104</v>
       </c>
       <c r="D61" s="124" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="E61" s="124" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="F61" s="151">
         <v>5000</v>
@@ -47791,7 +47805,7 @@
     </row>
     <row r="62" spans="1:8">
       <c r="A62" s="124" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B62" s="200">
         <v>54</v>
@@ -47800,10 +47814,10 @@
         <v>54</v>
       </c>
       <c r="D62" s="124" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="E62" s="124" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="F62" s="151">
         <v>2000</v>
@@ -47817,7 +47831,7 @@
     </row>
     <row r="63" spans="1:8">
       <c r="A63" s="124" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B63" s="200">
         <v>74</v>
@@ -47826,10 +47840,10 @@
         <v>74</v>
       </c>
       <c r="D63" s="124" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="E63" s="124" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="F63" s="151">
         <v>3000</v>
@@ -47843,7 +47857,7 @@
     </row>
     <row r="64" spans="1:8">
       <c r="A64" s="124" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B64" s="200">
         <v>94</v>
@@ -47852,10 +47866,10 @@
         <v>94</v>
       </c>
       <c r="D64" s="124" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="E64" s="124" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="F64" s="151">
         <v>4000</v>
@@ -47869,7 +47883,7 @@
     </row>
     <row r="65" spans="1:8">
       <c r="A65" s="124" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B65" s="200">
         <v>144</v>
@@ -47878,10 +47892,10 @@
         <v>144</v>
       </c>
       <c r="D65" s="124" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="E65" s="124" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="F65" s="151">
         <v>6000</v>
@@ -47895,7 +47909,7 @@
     </row>
     <row r="66" spans="1:8">
       <c r="A66" s="124" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B66" s="200">
         <v>62</v>
@@ -47904,10 +47918,10 @@
         <v>92</v>
       </c>
       <c r="D66" s="124" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="E66" s="124" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="F66" s="151">
         <v>6000</v>
@@ -47921,7 +47935,7 @@
     </row>
     <row r="67" spans="1:8">
       <c r="A67" s="124" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B67" s="200">
         <v>62</v>
@@ -47930,10 +47944,10 @@
         <v>67</v>
       </c>
       <c r="D67" s="124" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="E67" s="124" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="F67" s="151">
         <v>4000</v>
@@ -47947,7 +47961,7 @@
     </row>
     <row r="68" spans="1:8">
       <c r="A68" s="124" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B68" s="200">
         <v>42</v>
@@ -47956,10 +47970,10 @@
         <v>66</v>
       </c>
       <c r="D68" s="124" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="E68" s="124" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="F68" s="151">
         <v>4500</v>
@@ -47973,7 +47987,7 @@
     </row>
     <row r="69" spans="1:8">
       <c r="A69" s="124" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B69" s="200">
         <v>42</v>
@@ -47982,10 +47996,10 @@
         <v>47</v>
       </c>
       <c r="D69" s="124" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="E69" s="124" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="F69" s="151">
         <v>3000</v>
@@ -47999,7 +48013,7 @@
     </row>
     <row r="70" spans="1:8" ht="28.5">
       <c r="A70" s="124" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B70" s="200">
         <v>45</v>
@@ -48008,10 +48022,10 @@
         <v>202</v>
       </c>
       <c r="D70" s="124" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E70" s="124" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="F70" s="151">
         <v>6000</v>
@@ -48025,7 +48039,7 @@
     </row>
     <row r="71" spans="1:8" ht="28.5">
       <c r="A71" s="124" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B71" s="200">
         <v>45</v>
@@ -48034,10 +48048,10 @@
         <v>202</v>
       </c>
       <c r="D71" s="124" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="E71" s="124" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="F71" s="151">
         <v>8000</v>
@@ -48051,7 +48065,7 @@
     </row>
     <row r="72" spans="1:8" ht="28.5">
       <c r="A72" s="124" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B72" s="200">
         <v>57</v>
@@ -48060,10 +48074,10 @@
         <v>242</v>
       </c>
       <c r="D72" s="124" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E72" s="124" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="F72" s="151">
         <v>7000</v>
@@ -48077,7 +48091,7 @@
     </row>
     <row r="73" spans="1:8" ht="28.5">
       <c r="A73" s="124" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B73" s="200">
         <v>57</v>
@@ -48086,10 +48100,10 @@
         <v>242</v>
       </c>
       <c r="D73" s="124" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="E73" s="124" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="F73" s="151">
         <v>10000</v>
@@ -48103,15 +48117,15 @@
     </row>
     <row r="74" spans="1:8" ht="28.5">
       <c r="A74" s="124" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B74" s="200"/>
       <c r="C74" s="200"/>
       <c r="D74" s="124" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E74" s="124" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="F74" s="151">
         <v>0</v>
@@ -48125,7 +48139,7 @@
     </row>
     <row r="75" spans="1:8" ht="28.5">
       <c r="A75" s="124" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B75" s="200">
         <v>232</v>
@@ -48134,10 +48148,10 @@
         <v>232</v>
       </c>
       <c r="D75" s="124" t="s">
+        <v>453</v>
+      </c>
+      <c r="E75" s="124" t="s">
         <v>454</v>
-      </c>
-      <c r="E75" s="124" t="s">
-        <v>455</v>
       </c>
       <c r="F75" s="151">
         <v>8000</v>
@@ -48151,7 +48165,7 @@
     </row>
     <row r="76" spans="1:8" ht="28.5">
       <c r="A76" s="124" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B76" s="200">
         <v>232</v>
@@ -48160,10 +48174,10 @@
         <v>79</v>
       </c>
       <c r="D76" s="124" t="s">
+        <v>484</v>
+      </c>
+      <c r="E76" s="124" t="s">
         <v>485</v>
-      </c>
-      <c r="E76" s="124" t="s">
-        <v>486</v>
       </c>
       <c r="F76" s="151">
         <v>10000</v>
@@ -48177,7 +48191,7 @@
     </row>
     <row r="77" spans="1:8" ht="28.5">
       <c r="A77" s="124" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B77" s="200">
         <v>232</v>
@@ -48186,10 +48200,10 @@
         <v>254</v>
       </c>
       <c r="D77" s="124" t="s">
+        <v>484</v>
+      </c>
+      <c r="E77" s="124" t="s">
         <v>485</v>
-      </c>
-      <c r="E77" s="124" t="s">
-        <v>486</v>
       </c>
       <c r="F77" s="151">
         <v>15000</v>
@@ -48203,7 +48217,7 @@
     </row>
     <row r="78" spans="1:8" ht="28.5">
       <c r="A78" s="124" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B78" s="200">
         <v>232</v>
@@ -48212,10 +48226,10 @@
         <v>234</v>
       </c>
       <c r="D78" s="124" t="s">
+        <v>484</v>
+      </c>
+      <c r="E78" s="124" t="s">
         <v>485</v>
-      </c>
-      <c r="E78" s="124" t="s">
-        <v>486</v>
       </c>
       <c r="F78" s="151">
         <v>18000</v>
@@ -48229,7 +48243,7 @@
     </row>
     <row r="79" spans="1:8" ht="28.5">
       <c r="A79" s="124" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B79" s="200">
         <v>232</v>
@@ -48238,10 +48252,10 @@
         <v>304</v>
       </c>
       <c r="D79" s="124" t="s">
+        <v>484</v>
+      </c>
+      <c r="E79" s="124" t="s">
         <v>485</v>
-      </c>
-      <c r="E79" s="124" t="s">
-        <v>486</v>
       </c>
       <c r="F79" s="151">
         <v>20000</v>
@@ -48255,7 +48269,7 @@
     </row>
     <row r="80" spans="1:8" ht="28.5">
       <c r="A80" s="124" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B80" s="200">
         <v>232</v>
@@ -48264,10 +48278,10 @@
         <v>379</v>
       </c>
       <c r="D80" s="124" t="s">
+        <v>484</v>
+      </c>
+      <c r="E80" s="124" t="s">
         <v>485</v>
-      </c>
-      <c r="E80" s="124" t="s">
-        <v>486</v>
       </c>
       <c r="F80" s="151">
         <v>23000</v>
@@ -48281,7 +48295,7 @@
     </row>
     <row r="81" spans="1:8" ht="28.5">
       <c r="A81" s="124" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B81" s="200">
         <v>232</v>
@@ -48290,10 +48304,10 @@
         <v>454</v>
       </c>
       <c r="D81" s="124" t="s">
+        <v>484</v>
+      </c>
+      <c r="E81" s="124" t="s">
         <v>485</v>
-      </c>
-      <c r="E81" s="124" t="s">
-        <v>486</v>
       </c>
       <c r="F81" s="151">
         <v>25000</v>
@@ -48307,7 +48321,7 @@
     </row>
     <row r="82" spans="1:8" ht="42.75">
       <c r="A82" s="124" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B82" s="200">
         <v>32</v>
@@ -48316,10 +48330,10 @@
         <v>51</v>
       </c>
       <c r="D82" s="124" t="s">
+        <v>519</v>
+      </c>
+      <c r="E82" s="124" t="s">
         <v>520</v>
-      </c>
-      <c r="E82" s="124" t="s">
-        <v>521</v>
       </c>
       <c r="F82" s="151">
         <v>4000</v>
@@ -48333,7 +48347,7 @@
     </row>
     <row r="83" spans="1:8" ht="42.75">
       <c r="A83" s="124" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B83" s="200">
         <v>32</v>
@@ -48342,10 +48356,10 @@
         <v>100</v>
       </c>
       <c r="D83" s="124" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E83" s="124" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="F83" s="151">
         <v>4000</v>
@@ -48359,7 +48373,7 @@
     </row>
     <row r="84" spans="1:8" ht="28.5">
       <c r="A84" s="124" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B84" s="200">
         <v>74</v>
@@ -48368,10 +48382,10 @@
         <v>204</v>
       </c>
       <c r="D84" s="124" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="E84" s="124" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="F84" s="151">
         <v>6000</v>
@@ -48385,7 +48399,7 @@
     </row>
     <row r="85" spans="1:8" ht="28.5">
       <c r="A85" s="124" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B85" s="200">
         <v>74</v>
@@ -48394,10 +48408,10 @@
         <v>204</v>
       </c>
       <c r="D85" s="124" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="E85" s="124" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="F85" s="151">
         <v>6000</v>
@@ -48411,7 +48425,7 @@
     </row>
     <row r="86" spans="1:8" ht="28.5">
       <c r="A86" s="124" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B86" s="200">
         <v>74</v>
@@ -48420,10 +48434,10 @@
         <v>204</v>
       </c>
       <c r="D86" s="124" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="E86" s="124" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="F86" s="151">
         <v>6000</v>
@@ -48437,7 +48451,7 @@
     </row>
     <row r="87" spans="1:8">
       <c r="A87" s="124" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B87" s="200">
         <v>74</v>
@@ -48446,10 +48460,10 @@
         <v>204</v>
       </c>
       <c r="D87" s="124" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="E87" s="124" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="F87" s="151">
         <v>6000</v>
@@ -48463,7 +48477,7 @@
     </row>
     <row r="88" spans="1:8" ht="28.5">
       <c r="A88" s="124" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B88" s="200">
         <v>74</v>
@@ -48472,10 +48486,10 @@
         <v>204</v>
       </c>
       <c r="D88" s="124" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="E88" s="124" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="F88" s="151">
         <v>6000</v>
@@ -48489,7 +48503,7 @@
     </row>
     <row r="89" spans="1:8" ht="28.5">
       <c r="A89" s="124" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B89" s="200">
         <v>79</v>
@@ -48498,10 +48512,10 @@
         <v>224</v>
       </c>
       <c r="D89" s="124" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="E89" s="124" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="F89" s="151">
         <v>7000</v>
@@ -48515,7 +48529,7 @@
     </row>
     <row r="90" spans="1:8" ht="28.5">
       <c r="A90" s="124" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B90" s="200">
         <v>79</v>
@@ -48524,10 +48538,10 @@
         <v>224</v>
       </c>
       <c r="D90" s="124" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="E90" s="124" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="F90" s="151">
         <v>7000</v>
@@ -48541,7 +48555,7 @@
     </row>
     <row r="91" spans="1:8" ht="28.5">
       <c r="A91" s="124" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B91" s="200">
         <v>79</v>
@@ -48550,10 +48564,10 @@
         <v>224</v>
       </c>
       <c r="D91" s="124" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="E91" s="124" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="F91" s="151">
         <v>7000</v>
@@ -48567,7 +48581,7 @@
     </row>
     <row r="92" spans="1:8">
       <c r="A92" s="124" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B92" s="200">
         <v>79</v>
@@ -48576,10 +48590,10 @@
         <v>224</v>
       </c>
       <c r="D92" s="124" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="E92" s="124" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="F92" s="151">
         <v>7000</v>
@@ -48593,7 +48607,7 @@
     </row>
     <row r="93" spans="1:8" ht="28.5">
       <c r="A93" s="124" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B93" s="200">
         <v>79</v>
@@ -48602,10 +48616,10 @@
         <v>224</v>
       </c>
       <c r="D93" s="124" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="E93" s="124" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="F93" s="151">
         <v>7000</v>
@@ -48619,7 +48633,7 @@
     </row>
     <row r="94" spans="1:8" ht="28.5">
       <c r="A94" s="124" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B94" s="200">
         <v>94</v>
@@ -48628,10 +48642,10 @@
         <v>304</v>
       </c>
       <c r="D94" s="124" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="E94" s="124" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="F94" s="151">
         <v>8000</v>
@@ -48645,7 +48659,7 @@
     </row>
     <row r="95" spans="1:8" ht="28.5">
       <c r="A95" s="124" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B95" s="200">
         <v>94</v>
@@ -48654,10 +48668,10 @@
         <v>304</v>
       </c>
       <c r="D95" s="124" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="E95" s="124" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="F95" s="151">
         <v>8000</v>
@@ -48671,7 +48685,7 @@
     </row>
     <row r="96" spans="1:8" ht="28.5">
       <c r="A96" s="124" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B96" s="200">
         <v>94</v>
@@ -48680,10 +48694,10 @@
         <v>304</v>
       </c>
       <c r="D96" s="124" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="E96" s="124" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="F96" s="151">
         <v>8000</v>
@@ -48697,7 +48711,7 @@
     </row>
     <row r="97" spans="1:8">
       <c r="A97" s="124" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B97" s="200">
         <v>94</v>
@@ -48706,10 +48720,10 @@
         <v>304</v>
       </c>
       <c r="D97" s="124" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="E97" s="124" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="F97" s="151">
         <v>8000</v>
@@ -48723,7 +48737,7 @@
     </row>
     <row r="98" spans="1:8" ht="28.5">
       <c r="A98" s="124" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B98" s="200">
         <v>94</v>
@@ -48732,10 +48746,10 @@
         <v>304</v>
       </c>
       <c r="D98" s="124" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="E98" s="124" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="F98" s="151">
         <v>8000</v>
@@ -48749,7 +48763,7 @@
     </row>
     <row r="99" spans="1:8">
       <c r="A99" s="124" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B99" s="200"/>
       <c r="C99" s="200"/>
@@ -48767,7 +48781,7 @@
     </row>
     <row r="100" spans="1:8">
       <c r="A100" s="124" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B100" s="200"/>
       <c r="C100" s="200"/>
